--- a/Corrugated_Cost_Comparison.xlsx
+++ b/Corrugated_Cost_Comparison.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cost Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Volume" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Scenarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Order Totals" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Basis" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -20,10 +20,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="$#,##0.00;($#,##0.00);-"/>
-    <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
-    <numFmt numFmtId="166" formatCode="+0%;-0%"/>
+    <numFmt numFmtId="165" formatCode="+0%;-0%"/>
+    <numFmt numFmtId="166" formatCode="$#,##0;($#,##0);-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,21 +58,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -83,26 +68,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00006100"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="009C6500"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00006100"/>
       <sz val="10"/>
     </font>
     <font>
@@ -114,11 +79,17 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="009C6500"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -137,12 +108,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,17 +123,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -236,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -251,79 +217,55 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -414,7 +356,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Cost per box at 100 units - actual vs references (same quantity, same spec)</a:t>
+              <a:t>MEDIUM box - cost per box by order size</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -429,25 +371,41 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Cost Comparison'!C5</f>
+              <f>'Scenarios'!B5</f>
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
-            </a:solidFill>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
+                <a:srgbClr val="2A78D6"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="FFFFFF"/>
+              </a:bgClr>
+            </a:pattFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'Cost Comparison'!$A$6:$A$7</f>
+              <f>'Scenarios'!$B$5:$D$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cost Comparison'!$C$6:$C$7</f>
+              <f>'Scenarios'!$C$5:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -456,7 +414,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Cost Comparison'!D5</f>
+              <f>'Scenarios'!B6</f>
             </strRef>
           </tx>
           <spPr>
@@ -474,12 +432,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Cost Comparison'!$A$6:$A$7</f>
+              <f>'Scenarios'!$B$5:$D$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cost Comparison'!$D$6:$D$7</f>
+              <f>'Scenarios'!$C$6:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -488,37 +446,57 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Cost Comparison'!E5</f>
+              <f>'Scenarios'!B7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:pattFill prst="ltUpDiag">
-              <a:fgClr>
-                <a:srgbClr val="1BAF7A"/>
-              </a:fgClr>
-              <a:bgClr>
-                <a:srgbClr val="FFFFFF"/>
-              </a:bgClr>
-            </a:pattFill>
+            <a:solidFill>
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Cost Comparison'!$A$6:$A$7</f>
+              <f>'Scenarios'!$B$5:$D$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cost Comparison'!$E$6:$E$7</f>
+              <f>'Scenarios'!$C$7:$D$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios'!B8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenarios'!$B$5:$D$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios'!$C$8:$D$8</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
+          <numFmt formatCode="$#,##0.00"/>
           <showVal val="1"/>
         </dLbls>
-        <gapWidth val="60"/>
+        <gapWidth val="80"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -528,6 +506,21 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Order size (each)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -539,7 +532,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -581,34 +573,39 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>MEDIUM box 39 x 20 x 32 - cost per box by volume</a:t>
+              <a:t>LARGE box - cost per box by order size</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Volume'!B5</f>
+              <f>'Scenarios'!B35</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575">
-              <a:solidFill>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
                 <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="FFFFFF"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
+          <dPt>
+            <idx val="0"/>
             <spPr>
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
@@ -617,65 +614,109 @@
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
-          </marker>
+          </dPt>
           <cat>
             <numRef>
-              <f>'Volume'!$A$6:$A$11</f>
+              <f>'Scenarios'!$B$35:$D$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Volume'!$B$6:$B$11</f>
+              <f>'Scenarios'!$C$35:$D$35</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Volume'!C5</f>
+              <f>'Scenarios'!B36</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575">
-              <a:solidFill>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
                 <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:prstDash val="sysDot"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="FFFFFF"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Volume'!$A$6:$A$11</f>
+              <f>'Scenarios'!$B$35:$D$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Volume'!$C$6:$C$11</f>
+              <f>'Scenarios'!$C$36:$D$36</f>
             </numRef>
           </val>
-          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios'!B37</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenarios'!$B$35:$D$35</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios'!$C$37:$D$37</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios'!B38</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenarios'!$B$35:$D$35</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios'!$C$38:$D$38</f>
+            </numRef>
+          </val>
         </ser>
         <dLbls>
+          <numFmt formatCode="$#,##0.00"/>
           <showVal val="1"/>
         </dLbls>
+        <gapWidth val="80"/>
         <axId val="10"/>
         <axId val="100"/>
-      </lineChart>
+      </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -691,7 +732,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Quantity ordered (each)</a:t>
+                  <a:t>Order size (each)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -708,7 +749,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -750,101 +790,84 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>LARGE box 46 x 39 x 36 - cost per box by volume</a:t>
+              <a:t>Total order cost - the fixed block is identical in all three</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Volume'!D5</f>
+              <f>'Order Totals'!F5</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575">
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Volume'!$A$6:$A$11</f>
+              <f>'Order Totals'!$A$6:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Volume'!$D$6:$D$11</f>
+              <f>'Order Totals'!$F$6:$F$8</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Volume'!E5</f>
+              <f>'Order Totals'!G5</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575">
-              <a:solidFill>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
                 <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:prstDash val="sysDot"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="FFFFFF"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
           <cat>
             <numRef>
-              <f>'Volume'!$A$6:$A$11</f>
+              <f>'Order Totals'!$A$6:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Volume'!$E$6:$E$11</f>
+              <f>'Order Totals'!$G$6:$G$8</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <dLbls>
+          <numFmt formatCode="$#,##0"/>
           <showVal val="1"/>
         </dLbls>
+        <gapWidth val="90"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
-      </lineChart>
+      </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -860,7 +883,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Quantity ordered (each)</a:t>
+                  <a:t>Scenario</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -877,7 +900,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -887,7 +909,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>$ per box</a:t>
+                  <a:t>$ total order</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -913,37 +935,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7920000" cy="3780000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7920000" cy="3420000"/>
+    <ext cx="9360000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -962,10 +957,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7920000" cy="3420000"/>
+    <ext cx="9360000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -975,6 +970,33 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1272,36 +1294,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cost per box - what we pay today vs what it should cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
+          <t>Cost per box across three order sizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Everything on this sheet is at the SAME quantity: 100 of each box. Same board spec (48ECT kraft double wall), same two sizes, cost per box. Nothing is compared across different volumes.   SOLID = actual price we are charged.   HATCHED = not an actual price (an estimate, or a published catalogue price for a comparable box).</t>
+          <t>Three scenarios: 100, 250 and 1,000 of EACH box. Same board spec throughout (48ECT kraft double wall), cost per box, ex-freight. Within each scenario every figure is at the same quantity, so the comparison is like for like.   SOLID = a real price (what we are charged, or a published catalogue price).   HATCHED = not a real price (deduced or modelled).   Only ONE provider figure is an actual price: the 100-unit column. The 250 and 1,000 figures are deduced from it - see the Basis tab.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1.  THE COMPARISON - 100 units of each, cost per box</t>
+          <t>MEDIUM box  39 x 20 x 32 in  -  43.06 sq ft of board per box</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -1309,282 +1332,342 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
-      <c r="G4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="40" customHeight="1">
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Cost per box</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Board per box</t>
+          <t>100 each</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>PROVIDER  (actual)</t>
+          <t>250 each</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
+          <t>1,000 each</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Basis at 100</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Change 100 -&gt; 1,000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>PROVIDER - what we pay</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>ACTUAL invoice price</t>
+        </is>
+      </c>
+      <c r="F6" s="11">
+        <f>D6/B6-1</f>
+        <v>-0.6589645225</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
           <t>Independent estimate</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="B7" s="12" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Modelled from research</t>
+        </is>
+      </c>
+      <c r="F7" s="11">
+        <f>D7/B7-1</f>
+        <v>-0.4351458827</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Retail catalogue, same qty</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Difference vs estimate</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>MEDIUM  39 x 20 x 32</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>43.06</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>30.22</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="E6" s="10" t="n">
+      <c r="B8" s="12" t="n">
         <v>19.12</v>
       </c>
-      <c r="F6" s="11">
-        <f>C6-D6</f>
-        <v>16.23</v>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Materially above BOTH independent references. You can buy a comparable stock box off a catalogue shelf for less than we are charged for this one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>LARGE  46 x 39 x 36</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>89.19</v>
-      </c>
-      <c r="C7" s="9" t="n">
+      <c r="C8" s="12" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Published price</t>
+        </is>
+      </c>
+      <c r="F8" s="11">
+        <f>D8/B8-1</f>
+        <v>-0.1621621622</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>LARGE box  46 x 39 x 36 in  -  89.19 sq ft of board per box</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Cost per box</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>100 each</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>250 each</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>1,000 each</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Basis at 100</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Change 100 -&gt; 1,000</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>PROVIDER - what we pay</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n">
         <v>38.89</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="C36" s="9" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>ACTUAL invoice price</t>
+        </is>
+      </c>
+      <c r="F36" s="11">
+        <f>D36/B36-1</f>
+        <v>-0.5120572864</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Independent estimate</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n">
         <v>30.93</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="C37" s="12" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Modelled from research</t>
+        </is>
+      </c>
+      <c r="F37" s="11">
+        <f>D37/B37-1</f>
+        <v>-0.4040619607</v>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Retail catalogue, same qty</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n">
         <v>39.6</v>
       </c>
-      <c r="F7" s="11">
-        <f>C7-D7</f>
-        <v>7.96</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>Sits between the estimate and the catalogue price - i.e. right where it should be. No issue here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>2.  SAME THING PER SQUARE FOOT - so the two box sizes can be compared to each other</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Box</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>PROVIDER $/MSF (actual)</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Estimate $/MSF</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Catalogue $/MSF</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Provider vs catalogue</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM  39 x 20 x 32</t>
-        </is>
-      </c>
-      <c r="B32" s="14">
-        <f>30.2200/43.062500*1000</f>
-        <v>701.770682148</v>
-      </c>
-      <c r="C32" s="15">
-        <f>13.9900/43.062500*1000</f>
-        <v>324.8766328012</v>
-      </c>
-      <c r="D32" s="15" t="n">
-        <v>444</v>
-      </c>
-      <c r="E32" s="16">
-        <f>B32/D32-1</f>
-        <v>0.5805645994</v>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>LARGE  46 x 39 x 36</t>
-        </is>
-      </c>
-      <c r="B33" s="14">
-        <f>38.8900/89.192708*1000</f>
-        <v>436.022189781</v>
-      </c>
-      <c r="C33" s="15">
-        <f>30.9300/89.192708*1000</f>
-        <v>346.7772262774</v>
-      </c>
-      <c r="D33" s="15" t="n">
-        <v>444</v>
-      </c>
-      <c r="E33" s="17">
-        <f>B33/D33-1</f>
-        <v>-0.017968041</v>
-      </c>
-    </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Corrugated is sold by the MSF (thousand square feet of board), so this is the only fair way to compare a small box with a big one. The large box holds 2.07x the board of the medium but costs only 1.29x as much - which is why the two land so differently here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>3.  ONE THING TO CONFIRM BEFORE PRESENTING THIS</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>Does the provider's price include delivery?</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="20" t="inlineStr">
-        <is>
-          <t>It changes the LARGE box conclusion, though not the medium one:</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="19" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>If the price INCLUDES freight</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>Medium: $30.22 actual vs $17.26 estimate  (+75%)</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>Large: $38.89 actual vs $37.71 estimate  (+3%)</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="n"/>
-      <c r="G38" s="21" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>If the price EXCLUDES freight</t>
-        </is>
-      </c>
-      <c r="B39" s="21" t="n"/>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>Medium: $30.22 actual vs $13.99 estimate  (+116%)</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>Large: $38.89 actual vs $30.93 estimate  (+26%)</t>
-        </is>
-      </c>
-      <c r="F39" s="21" t="n"/>
-      <c r="G39" s="21" t="n"/>
+      <c r="C38" s="12" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>33.18</v>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Published price</t>
+        </is>
+      </c>
+      <c r="F38" s="11">
+        <f>D38/B38-1</f>
+        <v>-0.1621621622</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>WHAT THE THREE SCENARIOS SHOW</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="5" t="n"/>
+    </row>
+    <row r="65" ht="50" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>At 100 each - today</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="n"/>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>The MEDIUM box is the outlier: $30.22 against a catalogue price of $19.12 for a comparable stock box. We pay $11.10 more per box than we could buy one for. The LARGE box at $38.89 is already fractionally BELOW its catalogue equivalent, so there is no case to answer there.</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="n"/>
+      <c r="E65" s="14" t="n"/>
+      <c r="F65" s="14" t="n"/>
+      <c r="G65" s="14" t="n"/>
+      <c r="H65" s="14" t="n"/>
+    </row>
+    <row r="66" ht="50" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>At 250 each - the crossover</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="n"/>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>The medium box turns the corner: $16.94 against $17.27 catalogue. Essentially level. This is the point at which our provider stops being the expensive option on both boxes - and it only takes 150 more units of each.</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="n"/>
+      <c r="E66" s="14" t="n"/>
+      <c r="F66" s="14" t="n"/>
+      <c r="G66" s="14" t="n"/>
+      <c r="H66" s="14" t="n"/>
+    </row>
+    <row r="67" ht="50" customHeight="1">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>At 1,000 each - clearly good value</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="n"/>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Both boxes are well below catalogue: medium $10.31 vs $16.02, large $18.98 vs $33.18. Our provider's price falls 66% and 51% from the 100-unit level, while the catalogue price barely moves (-16%). That divergence is the whole argument.</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="n"/>
+      <c r="E67" s="14" t="n"/>
+      <c r="F67" s="14" t="n"/>
+      <c r="G67" s="14" t="n"/>
+      <c r="H67" s="14" t="n"/>
+    </row>
+    <row r="68" ht="50" customHeight="1">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>The conclusion</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n"/>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>This is not a supplier problem, it is an order-size problem. Our provider's underlying board rate works out at about $188/MSF, which is competitive. What makes 100 units look expensive is roughly $2,213 per SKU of fixed cost spread over too few boxes - and it lands hardest on the smaller box, because fixed cost does not care how big the box is.</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="n"/>
+      <c r="E68" s="14" t="n"/>
+      <c r="F68" s="14" t="n"/>
+      <c r="G68" s="14" t="n"/>
+      <c r="H68" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="E38:G38"/>
+  <mergeCells count="13">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C65:H65"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C66:H66"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="C67:H67"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="C68:H68"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -1597,36 +1680,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>How the comparison changes with volume</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
+          <t>What each scenario costs in total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Only ONE row here is an actual price: the provider at 100 units. Every other provider figure is DEDUCED from those two actual prices, and every estimate figure is MODELLED from public research. Both are labelled and drawn hatched or dashed so they are never mistaken for a quote. All figures ex-freight.</t>
+          <t>Same three scenarios, expressed as total spend rather than unit price. All provider figures; the 100 column is actual, the other two deduced. Ex-freight.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1.  COST PER BOX BY VOLUME</t>
+          <t>1.  TOTAL ORDER VALUE</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -1636,298 +1719,220 @@
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="5" t="n"/>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Qty each</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>MEDIUM - provider</t>
+          <t>Medium $/box</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>MEDIUM - estimate</t>
+          <t>Large $/box</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>LARGE - provider</t>
+          <t>$ per set</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>LARGE - estimate</t>
+          <t>TOTAL ORDER</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Provider basis</t>
+          <t>of which board</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Order total, provider</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" s="23" t="n">
+          <t>of which fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>100 of each</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
         <v>30.22</v>
       </c>
-      <c r="C6" s="24" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="D6" s="23" t="n">
+      <c r="C6" s="16" t="n">
         <v>38.89</v>
       </c>
-      <c r="E6" s="24" t="n">
-        <v>30.93</v>
-      </c>
-      <c r="F6" s="25" t="inlineStr">
-        <is>
-          <t>ACTUAL QUOTE</t>
-        </is>
-      </c>
-      <c r="G6" s="26">
-        <f>A6*(B6+D6)</f>
+      <c r="D6" s="16">
+        <f>B6+C6</f>
+        <v>69.11</v>
+      </c>
+      <c r="E6" s="17">
+        <f>100*D6</f>
         <v>6911.0</v>
       </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="27" t="n">
-        <v>250</v>
-      </c>
-      <c r="B7" s="28" t="n">
+      <c r="F6" s="17" t="n">
+        <v>2486</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>4425</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>250 of each</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
         <v>16.94</v>
       </c>
-      <c r="C7" s="10" t="n">
-        <v>11.37</v>
-      </c>
-      <c r="D7" s="28" t="n">
+      <c r="C7" s="12" t="n">
         <v>25.61</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>26.02</v>
-      </c>
-      <c r="F7" s="29" t="inlineStr">
-        <is>
-          <t>deduced</t>
-        </is>
-      </c>
-      <c r="G7" s="15">
-        <f>A7*(B7+D7)</f>
+      <c r="D7" s="12">
+        <f>B7+C7</f>
+        <v>42.5581228407</v>
+      </c>
+      <c r="E7" s="19">
+        <f>250*D7</f>
         <v>10639.5307101727</v>
       </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="27" t="n">
-        <v>500</v>
-      </c>
-      <c r="B8" s="28" t="n">
-        <v>12.52</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="D8" s="28" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>22.15</v>
-      </c>
-      <c r="F8" s="29" t="inlineStr">
-        <is>
-          <t>deduced</t>
-        </is>
-      </c>
-      <c r="G8" s="15">
-        <f>A8*(B8+D8)</f>
-        <v>16853.7485604607</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B9" s="28" t="n">
+      <c r="F7" s="19" t="n">
+        <v>6214</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>4425</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>1000 of each</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
         <v>10.31</v>
       </c>
-      <c r="C9" s="10" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="D9" s="28" t="n">
+      <c r="C8" s="12" t="n">
         <v>18.98</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="F9" s="29" t="inlineStr">
-        <is>
-          <t>deduced</t>
-        </is>
-      </c>
-      <c r="G9" s="15">
-        <f>A9*(B9+D9)</f>
+      <c r="D8" s="12">
+        <f>B8+C8</f>
+        <v>29.282184261</v>
+      </c>
+      <c r="E8" s="19">
+        <f>1000*D8</f>
         <v>29282.1842610365</v>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="27" t="n">
-        <v>2500</v>
-      </c>
-      <c r="B10" s="28" t="n">
-        <v>8.98</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="D10" s="28" t="n">
-        <v>17.65</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>15.94</v>
-      </c>
-      <c r="F10" s="29" t="inlineStr">
-        <is>
-          <t>deduced</t>
-        </is>
-      </c>
-      <c r="G10" s="15">
-        <f>A10*(B10+D10)</f>
-        <v>66567.4913627639</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="27" t="n">
-        <v>5000</v>
-      </c>
-      <c r="B11" s="28" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="D11" s="28" t="n">
-        <v>17.21</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F11" s="29" t="inlineStr">
-        <is>
-          <t>deduced</t>
-        </is>
-      </c>
-      <c r="G11" s="15">
-        <f>A11*(B11+D11)</f>
-        <v>128709.669865643</v>
-      </c>
-    </row>
-    <row r="51" ht="58" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>WHY BOTH LINES ARE DASHED. The only hard number on these charts is the provider's leftmost point - 100 units, the price we actually pay. The rest of the provider line is deduced by splitting those two actual prices into a board rate ($188/MSF) and a fixed charge ($2,213 per SKU), then re-spreading the fixed charge over larger runs. That split fits two unknowns to two data points, so it matches our prices exactly by construction - it is arithmetic, not evidence. Ask the provider to confirm their setup charge and the line becomes real.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>2.  WHAT THE VOLUME CONVERSATION IS WORTH</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="5" t="n"/>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>At 250 each instead of 100</t>
-        </is>
-      </c>
-      <c r="B54" s="21" t="n"/>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>Set drops from $69.11 to $42.56</t>
-        </is>
-      </c>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="30" t="inlineStr">
-        <is>
-          <t>38% less per unit</t>
-        </is>
-      </c>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="n"/>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>At 500 each instead of 100</t>
-        </is>
-      </c>
-      <c r="B55" s="21" t="n"/>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>Set drops from $69.11 to $33.71</t>
-        </is>
-      </c>
-      <c r="D55" s="21" t="n"/>
-      <c r="E55" s="30" t="inlineStr">
-        <is>
-          <t>51% less per unit</t>
-        </is>
-      </c>
-      <c r="F55" s="21" t="n"/>
-      <c r="G55" s="21" t="n"/>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>At 1000 each instead of 100</t>
-        </is>
-      </c>
-      <c r="B56" s="21" t="n"/>
-      <c r="C56" s="12" t="inlineStr">
-        <is>
-          <t>Set drops from $69.11 to $29.28</t>
-        </is>
-      </c>
-      <c r="D56" s="21" t="n"/>
-      <c r="E56" s="30" t="inlineStr">
-        <is>
-          <t>58% less per unit</t>
-        </is>
-      </c>
-      <c r="F56" s="21" t="n"/>
-      <c r="G56" s="21" t="n"/>
+      <c r="F8" s="19" t="n">
+        <v>24857</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>4425</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2.  WHAT THE EXTRA BOXES ACTUALLY COST</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Going from 100 to 250 each</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>150 more sets, costing $3,729 more in total</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="20">
+        <f> $24.86 per additional set</f>
+        <v/>
+      </c>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Going from 250 to 1000 each</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>750 more sets, costing $18,643 more in total</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="20">
+        <f> $24.86 per additional set</f>
+        <v/>
+      </c>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Going from 100 to 1000 each</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>900 more sets, costing $22,371 more in total</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="20">
+        <f> $24.86 per additional set</f>
+        <v/>
+      </c>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+    </row>
+    <row r="39" ht="52" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>THE SINGLE MOST USEFUL NUMBER HERE. Every additional set beyond the first order costs about $24.86, because the fixed charges are already paid. The first 100 sets cost $69.11 each only because they are carrying $4,425 of fixed cost between them. If there is any use at all for spare boxes - damage, a second run, buffer stock - the marginal ones are cheap in a way the headline price completely hides.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="A54:B54"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A34:G34"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -1940,26 +1945,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="98" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Basis of every figure - what is real and what is not</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
+          <t>Basis of every figure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Three categories only. ACTUAL means a price we are charged. PUBLISHED means someone else's price, printed and fetchable. DEDUCED or MODELLED means we worked it out and it carries uncertainty.</t>
+          <t>Four categories. ACTUAL is a price we are charged. PUBLISHED is someone else's printed price. CALCULATED is arithmetic with no uncertainty. DEDUCED or MODELLED means we worked it out.</t>
         </is>
       </c>
     </row>
@@ -1985,245 +1990,201 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="50" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Provider price, MEDIUM box, 100 units</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Provider price, MEDIUM, 100 each</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>$30.22</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>What we are charged today. Supplied by us, not researched.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Provider price, LARGE box, 100 units</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>What we are charged today. Supplied by us.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Provider price, LARGE, 100 each</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>$38.89</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>What we are charged today. Supplied by us, not researched.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Board area, MEDIUM box</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>43.06 sq ft</t>
-        </is>
-      </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>What we are charged today. Supplied by us.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Board area per box</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>43.06 / 89.19 sq ft</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>CALCULATED</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>From the drawing: blank = (2 x (39+20) + 1.25) x (32+20), divided by 144. Arithmetic, no uncertainty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Board area, LARGE box</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>89.19 sq ft</t>
-        </is>
-      </c>
-      <c r="C8" s="33" t="inlineStr">
-        <is>
-          <t>CALCULATED</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Same method: (2 x (46+39) + 1.25) x (36+39) / 144.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Retail catalogue price, 100 units</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>$444/MSF</t>
-        </is>
-      </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>From the drawings. Blank = (2 x (L+W) + 1.25) x (D+W), divided by 144. No uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Catalogue price, 100 / 250 / 1,000</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>$444 / $401 / $372 per MSF</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>PUBLISHED</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Median of 21 published catalogue prices for 275 lb test (= 48ECT) double wall boxes at a quantity of 100. 275 lb burst double wall is the equivalent grade to 48ECT on the standard tables, so these are comparable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Independent estimate, MEDIUM</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
-        <is>
-          <t>$13.99</t>
-        </is>
-      </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Medians of published catalogue prices for 275 lb test (= 48ECT) double wall boxes at each quantity - 21 prices at 100, 7 at 250, 6 at 1,000. Note how little it improves with volume: retail barely discounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Independent estimate</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>$290-$180 / $330-$205 per MSF</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>MODELLED</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Board at $290/MSF plus $150 setup over 100 units. The $290 comes from two independent routes agreeing - discounting catalogue prices by a distributor margin, and adjusting a real public-contract rate for double wall.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Independent estimate, LARGE</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>$30.93</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t>MODELLED</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Same method at $330/MSF - the large box carries a premium for its 75 in blank width.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Two independent routes agreeing: discounting catalogue prices by a distributor margin, and adjusting a real public-contract converter rate for double wall. Plus $150 setup per SKU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Provider marginal board rate</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>$188/MSF</t>
-        </is>
-      </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>$188 per MSF</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>(large price - medium price) / (large area - medium area). Notably competitive - it is in line with what a 500-1,000 piece converter price should look like, which is why the volume conversation matters more than switching supplier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Provider fixed charge per SKU</t>
-        </is>
-      </c>
-      <c r="B13" s="31" t="inlineStr">
-        <is>
-          <t>$2,213</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>(large price - medium price) / (large area - medium area). Competitive - in line with what a 500-1,000 piece converter price should be, which is why this reads as an order-size problem rather than a supplier problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Provider fixed charge</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>$2,213 per SKU</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>What remains of the medium-box price after its board is paid for, times 100. Assumes both boxes carry the same fixed charge and the same board rate - the natural reading if one provider quotes both, but an assumption. Confirm it by asking them to state setup separately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="50" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Provider prices at 250 units and above</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>see Volume tab</t>
-        </is>
-      </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>What is left of the medium-box price once its board is paid for, times 100. ASSUMES both boxes carry the same fixed charge and the same board rate - the natural reading if one provider quotes both, but an assumption. Confirm by asking them to state setup separately on the next quote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Provider prices at 250 and 1,000</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>see Scenarios tab</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Board rate and fixed charge re-spread over larger runs. Not quoted, not confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Freight, if applicable</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>$3.27 med / $6.78 lge</t>
-        </is>
-      </c>
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t>MODELLED</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Published Estes LTL tariff plus marketplace lane rates, Baltimore/Hagerstown to Sterling VA, for a shipment of 100 of each. The overlength surcharge does not apply - our longest flat piece is 85.6 in against a 96 in threshold.</t>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Board rate and fixed charge re-spread over the larger runs. Not quoted. Fitting two unknowns to two data points reproduces our actual prices by construction, so it is arithmetic rather than evidence - but the direction is not in doubt, because fixed cost provably does not scale with quantity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Freight</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>excluded throughout</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>All figures are ex-freight so they compare cleanly. For reference, delivery to Sterling VA on a 100-of-each order works out at about $3.27 per medium box and $6.78 per large. Confirm whether the provider's price already includes delivery - if it does, they are better value than shown here.</t>
         </is>
       </c>
     </row>

--- a/Corrugated_Cost_Comparison.xlsx
+++ b/Corrugated_Cost_Comparison.xlsx
@@ -477,6 +477,14 @@
             </strRef>
           </tx>
           <spPr>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
+                <a:srgbClr val="1BAF7A"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="FFFFFF"/>
+              </a:bgClr>
+            </a:pattFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -489,6 +497,30 @@
           <val>
             <numRef>
               <f>'Scenarios'!$C$8:$D$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios'!B9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenarios'!$B$5:$D$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios'!$C$9:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -588,7 +620,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!B35</f>
+              <f>'Scenarios'!B36</f>
             </strRef>
           </tx>
           <spPr>
@@ -617,12 +649,12 @@
           </dPt>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$35:$D$35</f>
+              <f>'Scenarios'!$B$36:$D$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$C$35:$D$35</f>
+              <f>'Scenarios'!$C$36:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -631,7 +663,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!B36</f>
+              <f>'Scenarios'!B37</f>
             </strRef>
           </tx>
           <spPr>
@@ -649,12 +681,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$35:$D$35</f>
+              <f>'Scenarios'!$B$36:$D$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$C$36:$D$36</f>
+              <f>'Scenarios'!$C$37:$D$37</f>
             </numRef>
           </val>
         </ser>
@@ -663,7 +695,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!B37</f>
+              <f>'Scenarios'!B38</f>
             </strRef>
           </tx>
           <spPr>
@@ -676,12 +708,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$35:$D$35</f>
+              <f>'Scenarios'!$B$36:$D$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$C$37:$D$37</f>
+              <f>'Scenarios'!$C$38:$D$38</f>
             </numRef>
           </val>
         </ser>
@@ -690,7 +722,39 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!B38</f>
+              <f>'Scenarios'!B39</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
+                <a:srgbClr val="1BAF7A"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="FFFFFF"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenarios'!$B$36:$D$36</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios'!$C$39:$D$39</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios'!B40</f>
             </strRef>
           </tx>
           <spPr>
@@ -700,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$35:$D$35</f>
+              <f>'Scenarios'!$B$36:$D$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$C$38:$D$38</f>
+              <f>'Scenarios'!$C$40:$D$40</f>
             </numRef>
           </val>
         </ser>
@@ -935,7 +999,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="4320000"/>
@@ -957,7 +1021,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="4320000"/>
@@ -1294,7 +1358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1422,211 +1486,225 @@
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Retail catalogue, same qty</t>
+          <t>Retail catalogue - LOW of range</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>19.12</v>
+        <v>17.17</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>17.27</v>
+        <v>16.45</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>16.02</v>
+        <v>15.2</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Published price</t>
+          <t>Published, cheapest comp</t>
         </is>
       </c>
       <c r="F8" s="11">
         <f>D8/B8-1</f>
-        <v>-0.1621621622</v>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+        <v>-0.1147730123</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Retail catalogue - HIGH of range</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Published, dearest comp</t>
+        </is>
+      </c>
+      <c r="F9" s="11">
+        <f>D9/B9-1</f>
+        <v>-0.115692829</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>LARGE box  46 x 39 x 36 in  -  89.19 sq ft of board per box</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Cost per box</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>100 each</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>250 each</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>1,000 each</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>Basis at 100</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>Change 100 -&gt; 1,000</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>PROVIDER - what we pay</t>
         </is>
       </c>
-      <c r="B36" s="8" t="n">
+      <c r="B37" s="8" t="n">
         <v>38.89</v>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C37" s="9" t="n">
         <v>25.61</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D37" s="9" t="n">
         <v>18.98</v>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>ACTUAL invoice price</t>
-        </is>
-      </c>
-      <c r="F36" s="11">
-        <f>D36/B36-1</f>
-        <v>-0.5120572864</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Independent estimate</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="n">
-        <v>30.93</v>
-      </c>
-      <c r="C37" s="12" t="n">
-        <v>26.02</v>
-      </c>
-      <c r="D37" s="12" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>Modelled from research</t>
         </is>
       </c>
       <c r="F37" s="11">
         <f>D37/B37-1</f>
-        <v>-0.4040619607</v>
+        <v>-0.5120572864</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Retail catalogue, same qty</t>
+          <t>Independent estimate</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>39.6</v>
+        <v>30.93</v>
       </c>
       <c r="C38" s="12" t="n">
-        <v>35.77</v>
+        <v>26.02</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>33.18</v>
+        <v>18.43</v>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>Published price</t>
+          <t>Modelled from research</t>
         </is>
       </c>
       <c r="F38" s="11">
         <f>D38/B38-1</f>
-        <v>-0.1621621622</v>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+        <v>-0.4040619607</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Retail catalogue - LOW of range</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Published, cheapest comp</t>
+        </is>
+      </c>
+      <c r="F39" s="11">
+        <f>D39/B39-1</f>
+        <v>-0.1147730123</v>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Retail catalogue - HIGH of range</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Published, dearest comp</t>
+        </is>
+      </c>
+      <c r="F40" s="11">
+        <f>D40/B40-1</f>
+        <v>-0.115692829</v>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>WHAT THE THREE SCENARIOS SHOW</t>
         </is>
       </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="5" t="n"/>
-    </row>
-    <row r="65" ht="50" customHeight="1">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>At 100 each - today</t>
-        </is>
-      </c>
-      <c r="B65" s="14" t="n"/>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>The MEDIUM box is the outlier: $30.22 against a catalogue price of $19.12 for a comparable stock box. We pay $11.10 more per box than we could buy one for. The LARGE box at $38.89 is already fractionally BELOW its catalogue equivalent, so there is no case to answer there.</t>
-        </is>
-      </c>
-      <c r="D65" s="14" t="n"/>
-      <c r="E65" s="14" t="n"/>
-      <c r="F65" s="14" t="n"/>
-      <c r="G65" s="14" t="n"/>
-      <c r="H65" s="14" t="n"/>
-    </row>
-    <row r="66" ht="50" customHeight="1">
-      <c r="A66" s="13" t="inlineStr">
-        <is>
-          <t>At 250 each - the crossover</t>
-        </is>
-      </c>
-      <c r="B66" s="14" t="n"/>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>The medium box turns the corner: $16.94 against $17.27 catalogue. Essentially level. This is the point at which our provider stops being the expensive option on both boxes - and it only takes 150 more units of each.</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="n"/>
-      <c r="E66" s="14" t="n"/>
-      <c r="F66" s="14" t="n"/>
-      <c r="G66" s="14" t="n"/>
-      <c r="H66" s="14" t="n"/>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="5" t="n"/>
     </row>
     <row r="67" ht="50" customHeight="1">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>At 1,000 each - clearly good value</t>
+          <t>At 100 each - today</t>
         </is>
       </c>
       <c r="B67" s="14" t="n"/>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Both boxes are well below catalogue: medium $10.31 vs $16.02, large $18.98 vs $33.18. Our provider's price falls 66% and 51% from the 100-unit level, while the catalogue price barely moves (-16%). That divergence is the whole argument.</t>
+          <t>The MEDIUM box is the outlier: $30.22 against a catalogue price of $17.99 for a comparable stock box. We pay $12.23 more per box than we could buy one for. The LARGE box at $38.89 is already fractionally BELOW its catalogue equivalent, so there is no case to answer there.</t>
         </is>
       </c>
       <c r="D67" s="14" t="n"/>
@@ -1638,13 +1716,13 @@
     <row r="68" ht="50" customHeight="1">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>The conclusion</t>
+          <t>At 250 each - the crossover</t>
         </is>
       </c>
       <c r="B68" s="14" t="n"/>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>This is not a supplier problem, it is an order-size problem. Our provider's underlying board rate works out at about $188/MSF, which is competitive. What makes 100 units look expensive is roughly $2,213 per SKU of fixed cost spread over too few boxes - and it lands hardest on the smaller box, because fixed cost does not care how big the box is.</t>
+          <t>The medium box drops to $16.94, inside its $16.45-$17.88 range. The large box at $25.61 falls clear BELOW its $34.07-$37.04 range. Both come good, and it takes only 150 more units of each to get here.</t>
         </is>
       </c>
       <c r="D68" s="14" t="n"/>
@@ -1653,21 +1731,57 @@
       <c r="G68" s="14" t="n"/>
       <c r="H68" s="14" t="n"/>
     </row>
+    <row r="69" ht="50" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>At 1,000 each - clearly good value</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="n"/>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Both boxes well below anything published: medium $10.31 vs $15.20-$16.63, large $18.98 vs $31.48-$34.45. Our price falls 66% and 51% from the 100-unit level while the published range moves only about 12% - retail discounts very little for volume, and that divergence is the whole argument.</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="n"/>
+      <c r="E69" s="14" t="n"/>
+      <c r="F69" s="14" t="n"/>
+      <c r="G69" s="14" t="n"/>
+      <c r="H69" s="14" t="n"/>
+    </row>
+    <row r="70" ht="50" customHeight="1">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>The conclusion</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="n"/>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>This is not a supplier problem, it is an order-size problem. Our provider's underlying board rate works out at about $188/MSF, which is competitive. What makes 100 units look expensive is roughly $2,213 per SKU of fixed cost spread over too few boxes - and it lands hardest on the smaller box, because fixed cost does not care how big the box is.</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="n"/>
+      <c r="E70" s="14" t="n"/>
+      <c r="F70" s="14" t="n"/>
+      <c r="G70" s="14" t="n"/>
+      <c r="H70" s="14" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="C65:H65"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="C66:H66"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A68:B68"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="C67:H67"/>
-    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C70:H70"/>
+    <mergeCell ref="C69:H69"/>
+    <mergeCell ref="A66:H66"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A70:B70"/>
     <mergeCell ref="A67:B67"/>
     <mergeCell ref="C68:H68"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C67:H67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -2059,12 +2173,12 @@
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Catalogue price, 100 / 250 / 1,000</t>
+          <t>Catalogue RANGE, 100 / 250 / 1,000</t>
         </is>
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>$444 / $401 / $372 per MSF</t>
+          <t>$399-437 / $382-415 / $353-386 per MSF</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -2074,7 +2188,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Medians of published catalogue prices for 275 lb test (= 48ECT) double wall boxes at each quantity - 21 prices at 100, 7 at 250, 6 at 1,000. Note how little it improves with volume: retail barely discounts.</t>
+          <t>Low and high across FIVE comparable 275 lb test (= 48ECT) double wall RSCs priced at each quantity tier. Shown as a range rather than a median because the spread is real: two retailers list the SAME 48x40x36 double-wall box at $33.59 and $45.95, a 37%% gap. Note also how little the range improves with volume - retail barely discounts.</t>
         </is>
       </c>
     </row>

--- a/Corrugated_Cost_Comparison.xlsx
+++ b/Corrugated_Cost_Comparison.xlsx
@@ -356,7 +356,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>MEDIUM box - cost per box by order size</a:t>
+              <a:t>MEDIUM box - cost per box by order size (catalogue = midpoint of published range)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -371,7 +371,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!B5</f>
+              <f>'Scenarios'!A6</f>
             </strRef>
           </tx>
           <spPr>
@@ -405,7 +405,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$C$5:$D$5</f>
+              <f>'Scenarios'!$B$6:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -414,7 +414,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!B6</f>
+              <f>'Scenarios'!A7</f>
             </strRef>
           </tx>
           <spPr>
@@ -437,7 +437,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$C$6:$D$6</f>
+              <f>'Scenarios'!$B$7:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -446,7 +446,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!B7</f>
+              <f>'Scenarios'!A8</f>
             </strRef>
           </tx>
           <spPr>
@@ -464,69 +464,18 @@
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$C$7:$D$7</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Scenarios'!B8</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:pattFill prst="ltUpDiag">
-              <a:fgClr>
-                <a:srgbClr val="1BAF7A"/>
-              </a:fgClr>
-              <a:bgClr>
-                <a:srgbClr val="FFFFFF"/>
-              </a:bgClr>
-            </a:pattFill>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Scenarios'!$B$5:$D$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Scenarios'!$C$8:$D$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'Scenarios'!B9</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Scenarios'!$B$5:$D$5</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Scenarios'!$C$9:$D$9</f>
+              <f>'Scenarios'!$B$8:$D$8</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
           <numFmt formatCode="$#,##0.00"/>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <gapWidth val="80"/>
         <axId val="10"/>
@@ -579,13 +528,15 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="$#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -605,7 +556,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>LARGE box - cost per box by order size</a:t>
+              <a:t>LARGE box - cost per box by order size (catalogue = midpoint of published range)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -620,7 +571,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!B36</f>
+              <f>'Scenarios'!A38</f>
             </strRef>
           </tx>
           <spPr>
@@ -649,12 +600,12 @@
           </dPt>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$36:$D$36</f>
+              <f>'Scenarios'!$B$37:$D$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$C$36:$D$36</f>
+              <f>'Scenarios'!$B$38:$D$38</f>
             </numRef>
           </val>
         </ser>
@@ -663,7 +614,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!B37</f>
+              <f>'Scenarios'!A39</f>
             </strRef>
           </tx>
           <spPr>
@@ -681,12 +632,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$36:$D$36</f>
+              <f>'Scenarios'!$B$37:$D$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$C$37:$D$37</f>
+              <f>'Scenarios'!$B$39:$D$39</f>
             </numRef>
           </val>
         </ser>
@@ -695,7 +646,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!B38</f>
+              <f>'Scenarios'!A40</f>
             </strRef>
           </tx>
           <spPr>
@@ -708,74 +659,23 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$36:$D$36</f>
+              <f>'Scenarios'!$B$37:$D$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$C$38:$D$38</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Scenarios'!B39</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:pattFill prst="ltUpDiag">
-              <a:fgClr>
-                <a:srgbClr val="1BAF7A"/>
-              </a:fgClr>
-              <a:bgClr>
-                <a:srgbClr val="FFFFFF"/>
-              </a:bgClr>
-            </a:pattFill>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Scenarios'!$B$36:$D$36</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Scenarios'!$C$39:$D$39</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'Scenarios'!B40</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Scenarios'!$B$36:$D$36</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Scenarios'!$C$40:$D$40</f>
+              <f>'Scenarios'!$B$40:$D$40</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
           <numFmt formatCode="$#,##0.00"/>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <gapWidth val="80"/>
         <axId val="10"/>
@@ -828,13 +728,15 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="$#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -925,7 +827,10 @@
         </ser>
         <dLbls>
           <numFmt formatCode="$#,##0"/>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
         </dLbls>
         <gapWidth val="90"/>
         <overlap val="100"/>
@@ -979,13 +884,15 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="$#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -999,10 +906,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4320000"/>
+    <ext cx="9360000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1021,10 +928,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="4320000"/>
+    <ext cx="9360000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1358,7 +1265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1486,261 +1393,275 @@
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Retail catalogue - LOW of range</t>
+          <t>Retail catalogue - mid of range</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="C8" s="12" t="n">
         <v>17.17</v>
       </c>
-      <c r="C8" s="12" t="n">
-        <v>16.45</v>
-      </c>
       <c r="D8" s="12" t="n">
-        <v>15.2</v>
+        <v>15.92</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Published, cheapest comp</t>
+          <t>Published, midpoint</t>
         </is>
       </c>
       <c r="F8" s="11">
         <f>D8/B8-1</f>
-        <v>-0.1147730123</v>
+        <v>-0.1152538721</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Retail catalogue - HIGH of range</t>
+          <t xml:space="preserve">   ...range low</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>18.81</v>
+        <v>17.17</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>17.88</v>
+        <v>16.45</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>16.63</v>
+        <v>15.2</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Published, dearest comp</t>
+          <t>Published, cheapest comp</t>
         </is>
       </c>
       <c r="F9" s="11">
         <f>D9/B9-1</f>
+        <v>-0.1147730123</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...range high</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Published, dearest comp</t>
+        </is>
+      </c>
+      <c r="F10" s="11">
+        <f>D10/B10-1</f>
         <v>-0.115692829</v>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>LARGE box  46 x 39 x 36 in  -  89.19 sq ft of board per box</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Cost per box</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>100 each</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>250 each</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>1,000 each</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>Basis at 100</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>Change 100 -&gt; 1,000</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>PROVIDER - what we pay</t>
         </is>
       </c>
-      <c r="B37" s="8" t="n">
+      <c r="B38" s="8" t="n">
         <v>38.89</v>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="C38" s="9" t="n">
         <v>25.61</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D38" s="9" t="n">
         <v>18.98</v>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>ACTUAL invoice price</t>
-        </is>
-      </c>
-      <c r="F37" s="11">
-        <f>D37/B37-1</f>
-        <v>-0.5120572864</v>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>Independent estimate</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n">
-        <v>30.93</v>
-      </c>
-      <c r="C38" s="12" t="n">
-        <v>26.02</v>
-      </c>
-      <c r="D38" s="12" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>Modelled from research</t>
         </is>
       </c>
       <c r="F38" s="11">
         <f>D38/B38-1</f>
-        <v>-0.4040619607</v>
+        <v>-0.5120572864</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Retail catalogue - LOW of range</t>
+          <t>Independent estimate</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>35.56</v>
+        <v>30.93</v>
       </c>
       <c r="C39" s="12" t="n">
-        <v>34.07</v>
+        <v>26.02</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>31.48</v>
+        <v>18.43</v>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Published, cheapest comp</t>
+          <t>Modelled from research</t>
         </is>
       </c>
       <c r="F39" s="11">
         <f>D39/B39-1</f>
-        <v>-0.1147730123</v>
+        <v>-0.4040619607</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Retail catalogue - HIGH of range</t>
+          <t>Retail catalogue - mid of range</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>38.96</v>
+        <v>37.26</v>
       </c>
       <c r="C40" s="12" t="n">
-        <v>37.04</v>
+        <v>35.56</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>34.45</v>
+        <v>32.96</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>Published, dearest comp</t>
+          <t>Published, midpoint</t>
         </is>
       </c>
       <c r="F40" s="11">
         <f>D40/B40-1</f>
+        <v>-0.1152538721</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...range low</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Published, cheapest comp</t>
+        </is>
+      </c>
+      <c r="F41" s="11">
+        <f>D41/B41-1</f>
+        <v>-0.1147730123</v>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...range high</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Published, dearest comp</t>
+        </is>
+      </c>
+      <c r="F42" s="11">
+        <f>D42/B42-1</f>
         <v>-0.115692829</v>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>WHAT THE THREE SCENARIOS SHOW</t>
         </is>
       </c>
-      <c r="B66" s="4" t="n"/>
-      <c r="C66" s="4" t="n"/>
-      <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="n"/>
-      <c r="F66" s="4" t="n"/>
-      <c r="G66" s="4" t="n"/>
-      <c r="H66" s="5" t="n"/>
-    </row>
-    <row r="67" ht="50" customHeight="1">
-      <c r="A67" s="13" t="inlineStr">
-        <is>
-          <t>At 100 each - today</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="n"/>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>The MEDIUM box is the outlier: $30.22 against a catalogue price of $17.99 for a comparable stock box. We pay $12.23 more per box than we could buy one for. The LARGE box at $38.89 is already fractionally BELOW its catalogue equivalent, so there is no case to answer there.</t>
-        </is>
-      </c>
-      <c r="D67" s="14" t="n"/>
-      <c r="E67" s="14" t="n"/>
-      <c r="F67" s="14" t="n"/>
-      <c r="G67" s="14" t="n"/>
-      <c r="H67" s="14" t="n"/>
-    </row>
-    <row r="68" ht="50" customHeight="1">
-      <c r="A68" s="13" t="inlineStr">
-        <is>
-          <t>At 250 each - the crossover</t>
-        </is>
-      </c>
-      <c r="B68" s="14" t="n"/>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>The medium box drops to $16.94, inside its $16.45-$17.88 range. The large box at $25.61 falls clear BELOW its $34.07-$37.04 range. Both come good, and it takes only 150 more units of each to get here.</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="n"/>
-      <c r="E68" s="14" t="n"/>
-      <c r="F68" s="14" t="n"/>
-      <c r="G68" s="14" t="n"/>
-      <c r="H68" s="14" t="n"/>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="5" t="n"/>
     </row>
     <row r="69" ht="50" customHeight="1">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>At 1,000 each - clearly good value</t>
+          <t>At 100 each - today</t>
         </is>
       </c>
       <c r="B69" s="14" t="n"/>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Both boxes well below anything published: medium $10.31 vs $15.20-$16.63, large $18.98 vs $31.48-$34.45. Our price falls 66% and 51% from the 100-unit level while the published range moves only about 12% - retail discounts very little for volume, and that divergence is the whole argument.</t>
+          <t>The MEDIUM box is the outlier: $30.22 against a catalogue price of $17.99 for a comparable stock box. We pay $12.23 more per box than we could buy one for. The LARGE box at $38.89 is already fractionally BELOW its catalogue equivalent, so there is no case to answer there.</t>
         </is>
       </c>
       <c r="D69" s="14" t="n"/>
@@ -1752,13 +1673,13 @@
     <row r="70" ht="50" customHeight="1">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>The conclusion</t>
+          <t>At 250 each - the crossover</t>
         </is>
       </c>
       <c r="B70" s="14" t="n"/>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>This is not a supplier problem, it is an order-size problem. Our provider's underlying board rate works out at about $188/MSF, which is competitive. What makes 100 units look expensive is roughly $2,213 per SKU of fixed cost spread over too few boxes - and it lands hardest on the smaller box, because fixed cost does not care how big the box is.</t>
+          <t>The medium box drops to $16.94, inside its $16.45-$17.88 range. The large box at $25.61 falls clear BELOW its $34.07-$37.04 range. Both come good, and it takes only 150 more units of each to get here.</t>
         </is>
       </c>
       <c r="D70" s="14" t="n"/>
@@ -1767,21 +1688,57 @@
       <c r="G70" s="14" t="n"/>
       <c r="H70" s="14" t="n"/>
     </row>
+    <row r="71" ht="50" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>At 1,000 each - clearly good value</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="n"/>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Both boxes well below anything published: medium $10.31 vs $15.20-$16.63, large $18.98 vs $31.48-$34.45. Our price falls 66% and 51% from the 100-unit level while the published range moves only about 12% - retail discounts very little for volume, and that divergence is the whole argument.</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="n"/>
+      <c r="E71" s="14" t="n"/>
+      <c r="F71" s="14" t="n"/>
+      <c r="G71" s="14" t="n"/>
+      <c r="H71" s="14" t="n"/>
+    </row>
+    <row r="72" ht="50" customHeight="1">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>The conclusion</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="n"/>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>This is not a supplier problem, it is an order-size problem. Our provider's underlying board rate works out at about $188/MSF, which is competitive. What makes 100 units look expensive is roughly $2,213 per SKU of fixed cost spread over too few boxes - and it lands hardest on the smaller box, because fixed cost does not care how big the box is.</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="n"/>
+      <c r="E72" s="14" t="n"/>
+      <c r="F72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C71:H71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:H72"/>
+    <mergeCell ref="A71:B71"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C70:H70"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="C69:H69"/>
-    <mergeCell ref="A66:H66"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="C68:H68"/>
     <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C67:H67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>

--- a/Corrugated_Cost_Comparison.xlsx
+++ b/Corrugated_Cost_Comparison.xlsx
@@ -89,7 +89,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -114,6 +114,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -202,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -232,6 +237,21 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -256,16 +276,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -756,6 +776,141 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Acceptable price at 100 units vs what we pay</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios'!A70</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenarios'!$B$69:$E$69</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios'!$B$70:$E$70</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios'!A71</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenarios'!$B$69:$E$69</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios'!$B$71:$E$71</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <numFmt formatCode="$#,##0.00"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
+        <gapWidth val="70"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>$ per box</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="$#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Total order cost - the fixed block is identical in all three</a:t>
             </a:r>
           </a:p>
@@ -941,6 +1096,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1265,7 +1442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1641,7 +1818,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>WHAT THE THREE SCENARIOS SHOW</t>
+          <t>ACCEPTABLE PRICE AT 100 UNITS - and where we actually sit</t>
         </is>
       </c>
       <c r="B68" s="4" t="n"/>
@@ -1652,93 +1829,222 @@
       <c r="G68" s="4" t="n"/>
       <c r="H68" s="5" t="n"/>
     </row>
-    <row r="69" ht="50" customHeight="1">
-      <c r="A69" s="13" t="inlineStr">
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Box</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Floor</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Ceiling</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>WE PAY</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>vs ceiling</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>vs target</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>MEDIUM 39 x 20 x 32</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="C70" s="12" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D70" s="12" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="E70" s="13" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="F70" s="14">
+        <f>E70-D70</f>
+        <v>11.4120225</v>
+      </c>
+      <c r="G70" s="12">
+        <f>E70-C70</f>
+        <v>13.82194875</v>
+      </c>
+      <c r="H70" s="15" t="inlineStr">
+        <is>
+          <t>OVER the ceiling - renegotiate</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>LARGE 46 x 39 x 36</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="n">
+        <v>30.93</v>
+      </c>
+      <c r="C71" s="12" t="n">
+        <v>34.94</v>
+      </c>
+      <c r="D71" s="12" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="E71" s="13" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="F71" s="16">
+        <f>E71-D71</f>
+        <v>-0.0658072917</v>
+      </c>
+      <c r="G71" s="12">
+        <f>E71-C71</f>
+        <v>3.9452994792</v>
+      </c>
+      <c r="H71" s="17" t="inlineStr">
+        <is>
+          <t>Inside the range, but at the top</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="56" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>HOW THE RANGE IS DEFINED. The FLOOR is the independent converter-direct estimate - below it is implausible for a custom job. The CEILING is the dearest comparable box anyone publishes: pay more than that and we are paying above retail for custom work, which is never defensible. TARGET is the midpoint. Bringing both boxes to the ceiling saves $1,141 on the current order (17%); to target, $1,777 (26%). Almost all of it is the medium box.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>WHAT THE THREE SCENARIOS SHOW</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="n"/>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="n"/>
+      <c r="G96" s="4" t="n"/>
+      <c r="H96" s="5" t="n"/>
+    </row>
+    <row r="97" ht="50" customHeight="1">
+      <c r="A97" s="18" t="inlineStr">
         <is>
           <t>At 100 each - today</t>
         </is>
       </c>
-      <c r="B69" s="14" t="n"/>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="B97" s="19" t="n"/>
+      <c r="C97" s="10" t="inlineStr">
         <is>
           <t>The MEDIUM box is the outlier: $30.22 against a catalogue price of $17.99 for a comparable stock box. We pay $12.23 more per box than we could buy one for. The LARGE box at $38.89 is already fractionally BELOW its catalogue equivalent, so there is no case to answer there.</t>
         </is>
       </c>
-      <c r="D69" s="14" t="n"/>
-      <c r="E69" s="14" t="n"/>
-      <c r="F69" s="14" t="n"/>
-      <c r="G69" s="14" t="n"/>
-      <c r="H69" s="14" t="n"/>
-    </row>
-    <row r="70" ht="50" customHeight="1">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="D97" s="19" t="n"/>
+      <c r="E97" s="19" t="n"/>
+      <c r="F97" s="19" t="n"/>
+      <c r="G97" s="19" t="n"/>
+      <c r="H97" s="19" t="n"/>
+    </row>
+    <row r="98" ht="50" customHeight="1">
+      <c r="A98" s="18" t="inlineStr">
         <is>
           <t>At 250 each - the crossover</t>
         </is>
       </c>
-      <c r="B70" s="14" t="n"/>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="B98" s="19" t="n"/>
+      <c r="C98" s="10" t="inlineStr">
         <is>
           <t>The medium box drops to $16.94, inside its $16.45-$17.88 range. The large box at $25.61 falls clear BELOW its $34.07-$37.04 range. Both come good, and it takes only 150 more units of each to get here.</t>
         </is>
       </c>
-      <c r="D70" s="14" t="n"/>
-      <c r="E70" s="14" t="n"/>
-      <c r="F70" s="14" t="n"/>
-      <c r="G70" s="14" t="n"/>
-      <c r="H70" s="14" t="n"/>
-    </row>
-    <row r="71" ht="50" customHeight="1">
-      <c r="A71" s="13" t="inlineStr">
+      <c r="D98" s="19" t="n"/>
+      <c r="E98" s="19" t="n"/>
+      <c r="F98" s="19" t="n"/>
+      <c r="G98" s="19" t="n"/>
+      <c r="H98" s="19" t="n"/>
+    </row>
+    <row r="99" ht="50" customHeight="1">
+      <c r="A99" s="18" t="inlineStr">
         <is>
           <t>At 1,000 each - clearly good value</t>
         </is>
       </c>
-      <c r="B71" s="14" t="n"/>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="B99" s="19" t="n"/>
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>Both boxes well below anything published: medium $10.31 vs $15.20-$16.63, large $18.98 vs $31.48-$34.45. Our price falls 66% and 51% from the 100-unit level while the published range moves only about 12% - retail discounts very little for volume, and that divergence is the whole argument.</t>
         </is>
       </c>
-      <c r="D71" s="14" t="n"/>
-      <c r="E71" s="14" t="n"/>
-      <c r="F71" s="14" t="n"/>
-      <c r="G71" s="14" t="n"/>
-      <c r="H71" s="14" t="n"/>
-    </row>
-    <row r="72" ht="50" customHeight="1">
-      <c r="A72" s="13" t="inlineStr">
+      <c r="D99" s="19" t="n"/>
+      <c r="E99" s="19" t="n"/>
+      <c r="F99" s="19" t="n"/>
+      <c r="G99" s="19" t="n"/>
+      <c r="H99" s="19" t="n"/>
+    </row>
+    <row r="100" ht="50" customHeight="1">
+      <c r="A100" s="18" t="inlineStr">
         <is>
           <t>The conclusion</t>
         </is>
       </c>
-      <c r="B72" s="14" t="n"/>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="B100" s="19" t="n"/>
+      <c r="C100" s="10" t="inlineStr">
         <is>
           <t>This is not a supplier problem, it is an order-size problem. Our provider's underlying board rate works out at about $188/MSF, which is competitive. What makes 100 units look expensive is roughly $2,213 per SKU of fixed cost spread over too few boxes - and it lands hardest on the smaller box, because fixed cost does not care how big the box is.</t>
         </is>
       </c>
-      <c r="D72" s="14" t="n"/>
-      <c r="E72" s="14" t="n"/>
-      <c r="F72" s="14" t="n"/>
-      <c r="G72" s="14" t="n"/>
-      <c r="H72" s="14" t="n"/>
+      <c r="D100" s="19" t="n"/>
+      <c r="E100" s="19" t="n"/>
+      <c r="F100" s="19" t="n"/>
+      <c r="G100" s="19" t="n"/>
+      <c r="H100" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
+    <mergeCell ref="A94:H94"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="C71:H71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:H72"/>
-    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="C99:H99"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="A96:H96"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C70:H70"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="C97:H97"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="A36:H36"/>
-    <mergeCell ref="C69:H69"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C100:H100"/>
+    <mergeCell ref="A97:B97"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -1828,34 +2134,34 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>100 of each</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="21" t="n">
         <v>30.22</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="21" t="n">
         <v>38.89</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="21">
         <f>B6+C6</f>
         <v>69.11</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="22">
         <f>100*D6</f>
         <v>6911.0</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="22" t="n">
         <v>2486</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="22" t="n">
         <v>4425</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>250 of each</t>
         </is>
@@ -1870,19 +2176,19 @@
         <f>B7+C7</f>
         <v>42.5581228407</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="24">
         <f>250*D7</f>
         <v>10639.5307101727</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="24" t="n">
         <v>6214</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="24" t="n">
         <v>4425</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>1000 of each</t>
         </is>
@@ -1897,14 +2203,14 @@
         <f>B8+C8</f>
         <v>29.282184261</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="24">
         <f>1000*D8</f>
         <v>29282.1842610365</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="24" t="n">
         <v>24857</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="24" t="n">
         <v>4425</v>
       </c>
     </row>
@@ -1927,19 +2233,19 @@
           <t>Going from 100 to 250 each</t>
         </is>
       </c>
-      <c r="B35" s="14" t="n"/>
+      <c r="B35" s="19" t="n"/>
       <c r="C35" s="10" t="inlineStr">
         <is>
           <t>150 more sets, costing $3,729 more in total</t>
         </is>
       </c>
-      <c r="D35" s="14" t="n"/>
-      <c r="E35" s="20">
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="25">
         <f> $24.86 per additional set</f>
         <v/>
       </c>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="14" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="19" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
@@ -1947,19 +2253,19 @@
           <t>Going from 250 to 1000 each</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n"/>
+      <c r="B36" s="19" t="n"/>
       <c r="C36" s="10" t="inlineStr">
         <is>
           <t>750 more sets, costing $18,643 more in total</t>
         </is>
       </c>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="20">
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="25">
         <f> $24.86 per additional set</f>
         <v/>
       </c>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="14" t="n"/>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="19" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -1967,19 +2273,19 @@
           <t>Going from 100 to 1000 each</t>
         </is>
       </c>
-      <c r="B37" s="14" t="n"/>
+      <c r="B37" s="19" t="n"/>
       <c r="C37" s="10" t="inlineStr">
         <is>
           <t>900 more sets, costing $22,371 more in total</t>
         </is>
       </c>
-      <c r="D37" s="14" t="n"/>
-      <c r="E37" s="20">
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="25">
         <f> $24.86 per additional set</f>
         <v/>
       </c>
-      <c r="F37" s="14" t="n"/>
-      <c r="G37" s="14" t="n"/>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="19" t="n"/>
     </row>
     <row r="39" ht="52" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -2016,7 +2322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2067,12 +2373,12 @@
           <t>Provider price, MEDIUM, 100 each</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>$30.22</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
@@ -2089,12 +2395,12 @@
           <t>Provider price, LARGE, 100 each</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>$38.89</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
@@ -2111,12 +2417,12 @@
           <t>Board area per box</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>43.06 / 89.19 sq ft</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>CALCULATED</t>
         </is>
@@ -2133,12 +2439,12 @@
           <t>Catalogue RANGE, 100 / 250 / 1,000</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>$399-437 / $382-415 / $353-386 per MSF</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>PUBLISHED</t>
         </is>
@@ -2155,12 +2461,12 @@
           <t>Independent estimate</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>$290-$180 / $330-$205 per MSF</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>MODELLED</t>
         </is>
@@ -2177,12 +2483,12 @@
           <t>Provider marginal board rate</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>$188 per MSF</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
@@ -2199,12 +2505,12 @@
           <t>Provider fixed charge</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>$2,213 per SKU</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
@@ -2221,12 +2527,12 @@
           <t>Provider prices at 250 and 1,000</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>see Scenarios tab</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
@@ -2240,20 +2546,42 @@
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>Acceptable range at 100</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>med $13.99-$18.81 / lge $30.93-$38.96</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Floor is the independent converter-direct estimate; ceiling is the dearest comparable PUBLISHED box at the same quantity. Both ends come from figures already in this workbook rather than a judgement call. The medium box sits $11.41 above its ceiling; the large box $0.07 below its own - inside, but by seven cents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
           <t>Freight</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>excluded throughout</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>All figures are ex-freight so they compare cleanly. For reference, delivery to Sterling VA on a 100-of-each order works out at about $3.27 per medium box and $6.78 per large. Confirm whether the provider's price already includes delivery - if it does, they are better value than shown here.</t>
         </is>

--- a/Corrugated_Cost_Comparison.xlsx
+++ b/Corrugated_Cost_Comparison.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="+0%;-0%"/>
     <numFmt numFmtId="166" formatCode="$#,##0;($#,##0);-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,7 +73,19 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="004A3AA7"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="004A3AA7"/>
       <sz val="10"/>
     </font>
     <font>
@@ -118,12 +130,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -207,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,25 +246,34 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -267,25 +288,31 @@
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -440,7 +467,7 @@
           <spPr>
             <a:pattFill prst="ltUpDiag">
               <a:fgClr>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="4A3AA7"/>
               </a:fgClr>
               <a:bgClr>
                 <a:srgbClr val="FFFFFF"/>
@@ -450,6 +477,17 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4A3AA7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'Scenarios'!$B$5:$D$5</f>
@@ -470,6 +508,38 @@
             </strRef>
           </tx>
           <spPr>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
+                <a:srgbClr val="EB6834"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="FFFFFF"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenarios'!$B$5:$D$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios'!$B$8:$D$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios'!A9</f>
+            </strRef>
+          </tx>
+          <spPr>
             <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
@@ -484,7 +554,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$8:$D$8</f>
+              <f>'Scenarios'!$B$9:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -591,7 +661,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!A38</f>
+              <f>'Scenarios'!A39</f>
             </strRef>
           </tx>
           <spPr>
@@ -620,12 +690,12 @@
           </dPt>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$37:$D$37</f>
+              <f>'Scenarios'!$B$38:$D$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$38:$D$38</f>
+              <f>'Scenarios'!$B$39:$D$39</f>
             </numRef>
           </val>
         </ser>
@@ -634,7 +704,50 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!A39</f>
+              <f>'Scenarios'!A40</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
+                <a:srgbClr val="4A3AA7"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:srgbClr val="FFFFFF"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4A3AA7"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'Scenarios'!$B$38:$D$38</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios'!$B$40:$D$40</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios'!A41</f>
             </strRef>
           </tx>
           <spPr>
@@ -652,21 +765,21 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$37:$D$37</f>
+              <f>'Scenarios'!$B$38:$D$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$39:$D$39</f>
+              <f>'Scenarios'!$B$41:$D$41</f>
             </numRef>
           </val>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!A40</f>
+              <f>'Scenarios'!A42</f>
             </strRef>
           </tx>
           <spPr>
@@ -679,12 +792,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$37:$D$37</f>
+              <f>'Scenarios'!$B$38:$D$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$40:$D$40</f>
+              <f>'Scenarios'!$B$42:$D$42</f>
             </numRef>
           </val>
         </ser>
@@ -776,7 +889,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Acceptable price at 100 units vs what we pay</a:t>
+              <a:t>Acceptable range at 100 units - what we pay, and what OrCon quoted</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -791,7 +904,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!A70</f>
+              <f>'Scenarios'!A72</f>
             </strRef>
           </tx>
           <spPr>
@@ -804,12 +917,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$69:$E$69</f>
+              <f>'Scenarios'!$B$71:$F$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$70:$E$70</f>
+              <f>'Scenarios'!$B$72:$F$72</f>
             </numRef>
           </val>
         </ser>
@@ -818,12 +931,12 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!A71</f>
+              <f>'Scenarios'!A73</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
@@ -831,12 +944,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$69:$E$69</f>
+              <f>'Scenarios'!$B$71:$F$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$71:$E$71</f>
+              <f>'Scenarios'!$B$73:$F$73</f>
             </numRef>
           </val>
         </ser>
@@ -1061,7 +1174,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3960000"/>
@@ -1083,7 +1196,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3960000"/>
@@ -1105,7 +1218,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="3600000"/>
@@ -1442,7 +1555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1543,508 +1656,556 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Independent estimate</t>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ORCON - competing quote</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>11.37</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>7.9</v>
+        <v>14.94</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>14.73</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Modelled from research</t>
+          <t>ACTUAL quote at 100</t>
         </is>
       </c>
       <c r="F7" s="11">
         <f>D7/B7-1</f>
-        <v>-0.4351458827</v>
+        <v>-0.0137383677</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Retail catalogue - mid of range</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>17.17</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>15.92</v>
+          <t>Independent estimate</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>7.9</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Published, midpoint</t>
+          <t>Modelled from research</t>
         </is>
       </c>
       <c r="F8" s="11">
         <f>D8/B8-1</f>
-        <v>-0.1152538721</v>
+        <v>-0.4351458827</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ...range low</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n">
+          <t>Retail catalogue - mid of range</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="C9" s="14" t="n">
         <v>17.17</v>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>16.45</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>15.2</v>
+      <c r="D9" s="14" t="n">
+        <v>15.92</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Published, cheapest comp</t>
+          <t>Published, midpoint</t>
         </is>
       </c>
       <c r="F9" s="11">
         <f>D9/B9-1</f>
-        <v>-0.1147730123</v>
+        <v>-0.1152538721</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ...range high</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>18.81</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>16.63</v>
+          <t xml:space="preserve">   ...range low</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>15.2</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Published, dearest comp</t>
+          <t>Published, cheapest comp</t>
         </is>
       </c>
       <c r="F10" s="11">
         <f>D10/B10-1</f>
+        <v>-0.1147730123</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...range high</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Published, dearest comp</t>
+        </is>
+      </c>
+      <c r="F11" s="11">
+        <f>D11/B11-1</f>
         <v>-0.115692829</v>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>LARGE box  46 x 39 x 36 in  -  89.19 sq ft of board per box</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Cost per box</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>100 each</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>250 each</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>1,000 each</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>Basis at 100</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>Change 100 -&gt; 1,000</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>PROVIDER - what we pay</t>
         </is>
       </c>
-      <c r="B38" s="8" t="n">
+      <c r="B39" s="8" t="n">
         <v>38.89</v>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C39" s="9" t="n">
         <v>25.61</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D39" s="9" t="n">
         <v>18.98</v>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>ACTUAL invoice price</t>
-        </is>
-      </c>
-      <c r="F38" s="11">
-        <f>D38/B38-1</f>
-        <v>-0.5120572864</v>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>Independent estimate</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="n">
-        <v>30.93</v>
-      </c>
-      <c r="C39" s="12" t="n">
-        <v>26.02</v>
-      </c>
-      <c r="D39" s="12" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>Modelled from research</t>
         </is>
       </c>
       <c r="F39" s="11">
         <f>D39/B39-1</f>
-        <v>-0.4040619607</v>
+        <v>-0.5120572864</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>Retail catalogue - mid of range</t>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>ORCON - competing quote</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>37.26</v>
-      </c>
-      <c r="C40" s="12" t="n">
-        <v>35.56</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>32.96</v>
+        <v>30.7</v>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>30.49</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>Published, midpoint</t>
+          <t>ACTUAL quote at 100</t>
         </is>
       </c>
       <c r="F40" s="11">
         <f>D40/B40-1</f>
-        <v>-0.1152538721</v>
+        <v>-0.0066857073</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ...range low</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="n">
-        <v>35.56</v>
-      </c>
-      <c r="C41" s="12" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>31.48</v>
+          <t>Independent estimate</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>30.93</v>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>18.43</v>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Published, cheapest comp</t>
+          <t>Modelled from research</t>
         </is>
       </c>
       <c r="F41" s="11">
         <f>D41/B41-1</f>
-        <v>-0.1147730123</v>
+        <v>-0.4040619607</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ...range high</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="n">
-        <v>38.96</v>
-      </c>
-      <c r="C42" s="12" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="D42" s="12" t="n">
-        <v>34.45</v>
+          <t>Retail catalogue - mid of range</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>37.26</v>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>32.96</v>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>Published, dearest comp</t>
+          <t>Published, midpoint</t>
         </is>
       </c>
       <c r="F42" s="11">
         <f>D42/B42-1</f>
+        <v>-0.1152538721</v>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...range low</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Published, cheapest comp</t>
+        </is>
+      </c>
+      <c r="F43" s="11">
+        <f>D43/B43-1</f>
+        <v>-0.1147730123</v>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...range high</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Published, dearest comp</t>
+        </is>
+      </c>
+      <c r="F44" s="11">
+        <f>D44/B44-1</f>
         <v>-0.115692829</v>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>ACCEPTABLE PRICE AT 100 UNITS - and where we actually sit</t>
         </is>
       </c>
-      <c r="B68" s="4" t="n"/>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n"/>
-      <c r="H68" s="5" t="n"/>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="B70" s="4" t="n"/>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="4" t="n"/>
+      <c r="E70" s="4" t="n"/>
+      <c r="F70" s="4" t="n"/>
+      <c r="G70" s="4" t="n"/>
+      <c r="H70" s="5" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>Box</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>Ceiling</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>WE PAY</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>ORCON</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
         <is>
           <t>vs ceiling</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>vs target</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="H71" s="6" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="26" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>MEDIUM 39 x 20 x 32</t>
         </is>
       </c>
-      <c r="B70" s="12" t="n">
+      <c r="B72" s="14" t="n">
         <v>13.99</v>
       </c>
-      <c r="C70" s="12" t="n">
+      <c r="C72" s="14" t="n">
         <v>16.4</v>
       </c>
-      <c r="D70" s="12" t="n">
+      <c r="D72" s="14" t="n">
         <v>18.81</v>
       </c>
-      <c r="E70" s="13" t="n">
+      <c r="E72" s="15" t="n">
         <v>30.22</v>
       </c>
-      <c r="F70" s="14">
-        <f>E70-D70</f>
+      <c r="F72" s="16" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="G72" s="17">
+        <f>E72-D72</f>
         <v>11.4120225</v>
       </c>
-      <c r="G70" s="12">
-        <f>E70-C70</f>
-        <v>13.82194875</v>
-      </c>
-      <c r="H70" s="15" t="inlineStr">
-        <is>
-          <t>OVER the ceiling - renegotiate</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="26" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
+      <c r="H72" s="18" t="inlineStr">
+        <is>
+          <t>OVER the ceiling. OrCon is $15.28 cheaper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>LARGE 46 x 39 x 36</t>
         </is>
       </c>
-      <c r="B71" s="12" t="n">
+      <c r="B73" s="14" t="n">
         <v>30.93</v>
       </c>
-      <c r="C71" s="12" t="n">
+      <c r="C73" s="14" t="n">
         <v>34.94</v>
       </c>
-      <c r="D71" s="12" t="n">
+      <c r="D73" s="14" t="n">
         <v>38.96</v>
       </c>
-      <c r="E71" s="13" t="n">
+      <c r="E73" s="15" t="n">
         <v>38.89</v>
       </c>
-      <c r="F71" s="16">
-        <f>E71-D71</f>
+      <c r="F73" s="16" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="G73" s="19">
+        <f>E73-D73</f>
         <v>-0.0658072917</v>
       </c>
-      <c r="G71" s="12">
-        <f>E71-C71</f>
-        <v>3.9452994792</v>
-      </c>
-      <c r="H71" s="17" t="inlineStr">
-        <is>
-          <t>Inside the range, but at the top</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="56" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>Top of the range. OrCon is $8.19 cheaper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="56" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>HOW THE RANGE IS DEFINED. The FLOOR is the independent converter-direct estimate - below it is implausible for a custom job. The CEILING is the dearest comparable box anyone publishes: pay more than that and we are paying above retail for custom work, which is never defensible. TARGET is the midpoint. Bringing both boxes to the ceiling saves $1,141 on the current order (17%); to target, $1,777 (26%). Almost all of it is the medium box.</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>WHAT THE THREE SCENARIOS SHOW</t>
         </is>
       </c>
-      <c r="B96" s="4" t="n"/>
-      <c r="C96" s="4" t="n"/>
-      <c r="D96" s="4" t="n"/>
-      <c r="E96" s="4" t="n"/>
-      <c r="F96" s="4" t="n"/>
-      <c r="G96" s="4" t="n"/>
-      <c r="H96" s="5" t="n"/>
-    </row>
-    <row r="97" ht="50" customHeight="1">
-      <c r="A97" s="18" t="inlineStr">
+      <c r="B98" s="4" t="n"/>
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="n"/>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="n"/>
+      <c r="G98" s="4" t="n"/>
+      <c r="H98" s="5" t="n"/>
+    </row>
+    <row r="99" ht="50" customHeight="1">
+      <c r="A99" s="21" t="inlineStr">
         <is>
           <t>At 100 each - today</t>
         </is>
       </c>
-      <c r="B97" s="19" t="n"/>
-      <c r="C97" s="10" t="inlineStr">
+      <c r="B99" s="22" t="n"/>
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>The MEDIUM box is the outlier: $30.22 against a catalogue price of $17.99 for a comparable stock box. We pay $12.23 more per box than we could buy one for. The LARGE box at $38.89 is already fractionally BELOW its catalogue equivalent, so there is no case to answer there.</t>
         </is>
       </c>
-      <c r="D97" s="19" t="n"/>
-      <c r="E97" s="19" t="n"/>
-      <c r="F97" s="19" t="n"/>
-      <c r="G97" s="19" t="n"/>
-      <c r="H97" s="19" t="n"/>
-    </row>
-    <row r="98" ht="50" customHeight="1">
-      <c r="A98" s="18" t="inlineStr">
+      <c r="D99" s="22" t="n"/>
+      <c r="E99" s="22" t="n"/>
+      <c r="F99" s="22" t="n"/>
+      <c r="G99" s="22" t="n"/>
+      <c r="H99" s="22" t="n"/>
+    </row>
+    <row r="100" ht="50" customHeight="1">
+      <c r="A100" s="21" t="inlineStr">
         <is>
           <t>At 250 each - the crossover</t>
         </is>
       </c>
-      <c r="B98" s="19" t="n"/>
-      <c r="C98" s="10" t="inlineStr">
+      <c r="B100" s="22" t="n"/>
+      <c r="C100" s="10" t="inlineStr">
         <is>
           <t>The medium box drops to $16.94, inside its $16.45-$17.88 range. The large box at $25.61 falls clear BELOW its $34.07-$37.04 range. Both come good, and it takes only 150 more units of each to get here.</t>
         </is>
       </c>
-      <c r="D98" s="19" t="n"/>
-      <c r="E98" s="19" t="n"/>
-      <c r="F98" s="19" t="n"/>
-      <c r="G98" s="19" t="n"/>
-      <c r="H98" s="19" t="n"/>
-    </row>
-    <row r="99" ht="50" customHeight="1">
-      <c r="A99" s="18" t="inlineStr">
+      <c r="D100" s="22" t="n"/>
+      <c r="E100" s="22" t="n"/>
+      <c r="F100" s="22" t="n"/>
+      <c r="G100" s="22" t="n"/>
+      <c r="H100" s="22" t="n"/>
+    </row>
+    <row r="101" ht="50" customHeight="1">
+      <c r="A101" s="21" t="inlineStr">
         <is>
           <t>At 1,000 each - clearly good value</t>
         </is>
       </c>
-      <c r="B99" s="19" t="n"/>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="B101" s="22" t="n"/>
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>Both boxes well below anything published: medium $10.31 vs $15.20-$16.63, large $18.98 vs $31.48-$34.45. Our price falls 66% and 51% from the 100-unit level while the published range moves only about 12% - retail discounts very little for volume, and that divergence is the whole argument.</t>
         </is>
       </c>
-      <c r="D99" s="19" t="n"/>
-      <c r="E99" s="19" t="n"/>
-      <c r="F99" s="19" t="n"/>
-      <c r="G99" s="19" t="n"/>
-      <c r="H99" s="19" t="n"/>
-    </row>
-    <row r="100" ht="50" customHeight="1">
-      <c r="A100" s="18" t="inlineStr">
+      <c r="D101" s="22" t="n"/>
+      <c r="E101" s="22" t="n"/>
+      <c r="F101" s="22" t="n"/>
+      <c r="G101" s="22" t="n"/>
+      <c r="H101" s="22" t="n"/>
+    </row>
+    <row r="102" ht="50" customHeight="1">
+      <c r="A102" s="21" t="inlineStr">
         <is>
           <t>The conclusion</t>
         </is>
       </c>
-      <c r="B100" s="19" t="n"/>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="B102" s="22" t="n"/>
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>This is not a supplier problem, it is an order-size problem. Our provider's underlying board rate works out at about $188/MSF, which is competitive. What makes 100 units look expensive is roughly $2,213 per SKU of fixed cost spread over too few boxes - and it lands hardest on the smaller box, because fixed cost does not care how big the box is.</t>
         </is>
       </c>
-      <c r="D100" s="19" t="n"/>
-      <c r="E100" s="19" t="n"/>
-      <c r="F100" s="19" t="n"/>
-      <c r="G100" s="19" t="n"/>
-      <c r="H100" s="19" t="n"/>
+      <c r="D102" s="22" t="n"/>
+      <c r="E102" s="22" t="n"/>
+      <c r="F102" s="22" t="n"/>
+      <c r="G102" s="22" t="n"/>
+      <c r="H102" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A94:H94"/>
+    <mergeCell ref="A70:H70"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A101:B101"/>
     <mergeCell ref="C99:H99"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="C98:H98"/>
     <mergeCell ref="A96:H96"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A99:B99"/>
-    <mergeCell ref="C97:H97"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="C102:H102"/>
+    <mergeCell ref="A98:H98"/>
+    <mergeCell ref="C101:H101"/>
+    <mergeCell ref="A102:B102"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="C100:H100"/>
-    <mergeCell ref="A97:B97"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -2104,113 +2265,113 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Medium $/box</t>
+          <t>Us $ per set</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Large $/box</t>
+          <t>Us TOTAL</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>$ per set</t>
+          <t>OrCon $ per set</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>TOTAL ORDER</t>
+          <t>OrCon TOTAL</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>of which board</t>
+          <t>of which board (us)</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>of which fixed</t>
+          <t>of which fixed (us)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>100 of each</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n">
-        <v>30.22</v>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>38.89</v>
-      </c>
-      <c r="D6" s="21">
-        <f>B6+C6</f>
+      <c r="B6" s="24" t="n">
         <v>69.11</v>
       </c>
-      <c r="E6" s="22">
+      <c r="C6" s="25">
+        <f>100*B6</f>
+        <v>6911.0</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="E6" s="25">
         <f>100*D6</f>
-        <v>6911.0</v>
-      </c>
-      <c r="F6" s="22" t="n">
+        <v>4564.0</v>
+      </c>
+      <c r="F6" s="25" t="n">
         <v>2486</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="25" t="n">
         <v>4425</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>250 of each</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>25.61</v>
-      </c>
-      <c r="D7" s="12">
-        <f>B7+C7</f>
-        <v>42.5581228407</v>
-      </c>
-      <c r="E7" s="24">
+      <c r="B7" s="14" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="C7" s="28">
+        <f>250*B7</f>
+        <v>10639.5307101727</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="E7" s="28">
         <f>250*D7</f>
-        <v>10639.5307101727</v>
-      </c>
-      <c r="F7" s="24" t="n">
+        <v>11341.5829287569</v>
+      </c>
+      <c r="F7" s="28" t="n">
         <v>6214</v>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="28" t="n">
         <v>4425</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>1000 of each</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="D8" s="12">
-        <f>B8+C8</f>
-        <v>29.282184261</v>
-      </c>
-      <c r="E8" s="24">
+      <c r="B8" s="14" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="C8" s="28">
+        <f>1000*B8</f>
+        <v>29282.1842610365</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="E8" s="28">
         <f>1000*D8</f>
-        <v>29282.1842610365</v>
-      </c>
-      <c r="F8" s="24" t="n">
+        <v>45229.4975725415</v>
+      </c>
+      <c r="F8" s="28" t="n">
         <v>24857</v>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="28" t="n">
         <v>4425</v>
       </c>
     </row>
@@ -2233,19 +2394,19 @@
           <t>Going from 100 to 250 each</t>
         </is>
       </c>
-      <c r="B35" s="19" t="n"/>
+      <c r="B35" s="22" t="n"/>
       <c r="C35" s="10" t="inlineStr">
         <is>
           <t>150 more sets, costing $3,729 more in total</t>
         </is>
       </c>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="25">
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="30">
         <f> $24.86 per additional set</f>
         <v/>
       </c>
-      <c r="F35" s="19" t="n"/>
-      <c r="G35" s="19" t="n"/>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
@@ -2253,19 +2414,19 @@
           <t>Going from 250 to 1000 each</t>
         </is>
       </c>
-      <c r="B36" s="19" t="n"/>
+      <c r="B36" s="22" t="n"/>
       <c r="C36" s="10" t="inlineStr">
         <is>
           <t>750 more sets, costing $18,643 more in total</t>
         </is>
       </c>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="25">
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="30">
         <f> $24.86 per additional set</f>
         <v/>
       </c>
-      <c r="F36" s="19" t="n"/>
-      <c r="G36" s="19" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="22" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -2273,19 +2434,19 @@
           <t>Going from 100 to 1000 each</t>
         </is>
       </c>
-      <c r="B37" s="19" t="n"/>
+      <c r="B37" s="22" t="n"/>
       <c r="C37" s="10" t="inlineStr">
         <is>
           <t>900 more sets, costing $22,371 more in total</t>
         </is>
       </c>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="25">
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="30">
         <f> $24.86 per additional set</f>
         <v/>
       </c>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="19" t="n"/>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="22" t="n"/>
     </row>
     <row r="39" ht="52" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -2322,7 +2483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2373,12 +2534,12 @@
           <t>Provider price, MEDIUM, 100 each</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>$30.22</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
@@ -2395,12 +2556,12 @@
           <t>Provider price, LARGE, 100 each</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>$38.89</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
@@ -2417,12 +2578,12 @@
           <t>Board area per box</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>43.06 / 89.19 sq ft</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>CALCULATED</t>
         </is>
@@ -2439,12 +2600,12 @@
           <t>Catalogue RANGE, 100 / 250 / 1,000</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>$399-437 / $382-415 / $353-386 per MSF</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>PUBLISHED</t>
         </is>
@@ -2461,12 +2622,12 @@
           <t>Independent estimate</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>$290-$180 / $330-$205 per MSF</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>MODELLED</t>
         </is>
@@ -2483,12 +2644,12 @@
           <t>Provider marginal board rate</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>$188 per MSF</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
@@ -2505,12 +2666,12 @@
           <t>Provider fixed charge</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>$2,213 per SKU</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
@@ -2527,12 +2688,12 @@
           <t>Provider prices at 250 and 1,000</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>see Scenarios tab</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
@@ -2546,42 +2707,108 @@
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Acceptable range at 100</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>med $13.99-$18.81 / lge $30.93-$38.96</t>
-        </is>
-      </c>
-      <c r="C13" s="28" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+          <t>OrCon quote, 100 each</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>med $14.94 / lge $30.70</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>ACTUAL</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Floor is the independent converter-direct estimate; ceiling is the dearest comparable PUBLISHED box at the same quantity. Both ends come from figures already in this workbook rather than a judgement call. The medium box sits $11.41 above its ceiling; the large box $0.07 below its own - inside, but by seven cents.</t>
+          <t>A real competing quote for the identical spec - RSC, 48 ECT kraft double wall, 75/pallet, 100 each. Works out at $347 and $344 per MSF: the SAME rate on both boxes, which is what a quote looks like when it is board times area. Ours varies 61%% between the two, which is the fixed charge showing through.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>OrCon pricing structure</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>$342/MSF + ~$23 fixed per SKU</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>DEDUCED</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Split the same way as ours. OrCon carries essentially NO setup charge but a higher board rate; we carry a low board rate and $2,213 of setup. Low volume favours no setup, high volume favours cheap board - so the two cross over near 215 units each. TREAT THAT CROSSOVER AS A QUESTION, NOT A FINDING: OrCon quoted one quantity only, and a supplier with no setup charge at 100 very likely discounts at volume, which the flat extrapolation ignores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Estimate validated against OrCon</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>within 7%% and 1%%</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>The modelled converter-direct price was $13.99 and $30.93, produced BEFORE this quote existed. OrCon came in at $14.94 and $30.70. The large box matched to under 1%%. That is a genuine out-of-sample check on the method.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Acceptable range at 100</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>med $13.99-$18.81 / lge $30.93-$38.96</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Floor is the independent converter-direct estimate; ceiling is the dearest comparable PUBLISHED box at the same quantity. Both ends come from figures already in this workbook rather than a judgement call. The medium box sits $11.41 above its ceiling; the large box $0.07 below its own - inside, but by seven cents. OrCon lands in the good zone on the medium box and just below the modelled floor on the large one, which says the floor was set at a realistic level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>Freight</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>excluded throughout</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>All figures are ex-freight so they compare cleanly. For reference, delivery to Sterling VA on a 100-of-each order works out at about $3.27 per medium box and $6.78 per large. Confirm whether the provider's price already includes delivery - if it does, they are better value than shown here.</t>
         </is>

--- a/Corrugated_Cost_Comparison.xlsx
+++ b/Corrugated_Cost_Comparison.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="+0%;-0%"/>
     <numFmt numFmtId="166" formatCode="$#,##0;($#,##0);-"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00C0501F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="10"/>
     </font>
@@ -86,6 +92,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="004A3AA7"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0501F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -219,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -252,6 +264,12 @@
     <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -261,19 +279,16 @@
     <xf numFmtId="164" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -288,7 +303,10 @@
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -297,22 +315,25 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -520,6 +541,17 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'Scenarios'!$B$5:$D$5</f>
@@ -536,7 +568,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!A9</f>
+              <f>'Scenarios'!A10</f>
             </strRef>
           </tx>
           <spPr>
@@ -554,7 +586,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$9:$D$9</f>
+              <f>'Scenarios'!$B$10:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -661,7 +693,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!A39</f>
+              <f>'Scenarios'!A40</f>
             </strRef>
           </tx>
           <spPr>
@@ -690,12 +722,12 @@
           </dPt>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$38:$D$38</f>
+              <f>'Scenarios'!$B$39:$D$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$39:$D$39</f>
+              <f>'Scenarios'!$B$40:$D$40</f>
             </numRef>
           </val>
         </ser>
@@ -704,7 +736,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!A40</f>
+              <f>'Scenarios'!A41</f>
             </strRef>
           </tx>
           <spPr>
@@ -733,12 +765,12 @@
           </dPt>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$38:$D$38</f>
+              <f>'Scenarios'!$B$39:$D$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$40:$D$40</f>
+              <f>'Scenarios'!$B$41:$D$41</f>
             </numRef>
           </val>
         </ser>
@@ -747,7 +779,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!A41</f>
+              <f>'Scenarios'!A42</f>
             </strRef>
           </tx>
           <spPr>
@@ -763,14 +795,25 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$38:$D$38</f>
+              <f>'Scenarios'!$B$39:$D$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$41:$D$41</f>
+              <f>'Scenarios'!$B$42:$D$42</f>
             </numRef>
           </val>
         </ser>
@@ -779,7 +822,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!A42</f>
+              <f>'Scenarios'!A44</f>
             </strRef>
           </tx>
           <spPr>
@@ -792,12 +835,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$38:$D$38</f>
+              <f>'Scenarios'!$B$39:$D$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$42:$D$42</f>
+              <f>'Scenarios'!$B$44:$D$44</f>
             </numRef>
           </val>
         </ser>
@@ -889,7 +932,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Acceptable range at 100 units - what we pay, and what OrCon quoted</a:t>
+              <a:t>At 100 units: acceptable range, what we pay, and both competing quotes (* Atlas projected from 250)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -904,7 +947,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!A72</f>
+              <f>'Scenarios'!A74</f>
             </strRef>
           </tx>
           <spPr>
@@ -917,12 +960,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$71:$F$71</f>
+              <f>'Scenarios'!$B$73:$G$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$72:$F$72</f>
+              <f>'Scenarios'!$B$74:$G$74</f>
             </numRef>
           </val>
         </ser>
@@ -931,7 +974,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!A73</f>
+              <f>'Scenarios'!A75</f>
             </strRef>
           </tx>
           <spPr>
@@ -944,12 +987,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$B$71:$F$71</f>
+              <f>'Scenarios'!$B$73:$G$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$73:$F$73</f>
+              <f>'Scenarios'!$B$75:$G$75</f>
             </numRef>
           </val>
         </ser>
@@ -1024,7 +1067,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Total order cost - the fixed block is identical in all three</a:t>
+              <a:t>Cost per set by supplier and order size (Atlas is a real quote at 250 only)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1033,13 +1076,13 @@
     <plotArea>
       <barChart>
         <barDir val="col"/>
-        <grouping val="stacked"/>
+        <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Order Totals'!F5</f>
+              <f>'Order Totals'!B5</f>
             </strRef>
           </tx>
           <spPr>
@@ -1057,7 +1100,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Order Totals'!$F$6:$F$8</f>
+              <f>'Order Totals'!$B$6:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -1066,18 +1109,13 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Order Totals'!G5</f>
+              <f>'Order Totals'!D5</f>
             </strRef>
           </tx>
           <spPr>
-            <a:pattFill prst="ltUpDiag">
-              <a:fgClr>
-                <a:srgbClr val="EB6834"/>
-              </a:fgClr>
-              <a:bgClr>
-                <a:srgbClr val="FFFFFF"/>
-              </a:bgClr>
-            </a:pattFill>
+            <a:solidFill>
+              <a:srgbClr val="4A3AA7"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1089,19 +1127,45 @@
           </cat>
           <val>
             <numRef>
-              <f>'Order Totals'!$G$6:$G$8</f>
+              <f>'Order Totals'!$D$6:$D$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Order Totals'!F5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Order Totals'!$A$6:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Order Totals'!$F$6:$F$8</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
-          <numFmt formatCode="$#,##0"/>
+          <numFmt formatCode="$#,##0.00"/>
           <showLegendKey val="0"/>
           <showVal val="1"/>
           <showCatName val="0"/>
           <showSerName val="0"/>
         </dLbls>
-        <gapWidth val="90"/>
-        <overlap val="100"/>
+        <gapWidth val="70"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -1174,7 +1238,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3960000"/>
@@ -1196,7 +1260,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3960000"/>
@@ -1218,7 +1282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="3600000"/>
@@ -1555,7 +1619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1681,531 +1745,579 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Independent estimate</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ATLAS - competing quote</t>
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>11.37</v>
+        <v>11.15</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>9.32</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>7.9</v>
+        <v>8.41</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Modelled from research</t>
+          <t>ACTUAL quote at 250 (MOQ)</t>
         </is>
       </c>
       <c r="F8" s="11">
         <f>D8/B8-1</f>
-        <v>-0.4351458827</v>
+        <v>-0.2457208226</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Retail catalogue - mid of range</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>17.17</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>15.92</v>
+          <t>Independent estimate</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>7.9</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Published, midpoint</t>
+          <t>Modelled from research</t>
         </is>
       </c>
       <c r="F9" s="11">
         <f>D9/B9-1</f>
-        <v>-0.1152538721</v>
+        <v>-0.4351458827</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ...range low</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
+          <t>Retail catalogue - mid of range</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="C10" s="16" t="n">
         <v>17.17</v>
       </c>
-      <c r="C10" s="14" t="n">
-        <v>16.45</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>15.2</v>
+      <c r="D10" s="16" t="n">
+        <v>15.92</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Published, cheapest comp</t>
+          <t>Published, midpoint</t>
         </is>
       </c>
       <c r="F10" s="11">
         <f>D10/B10-1</f>
-        <v>-0.1147730123</v>
+        <v>-0.1152538721</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ...range high</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>18.81</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>16.63</v>
+          <t xml:space="preserve">   ...range low</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>15.2</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Published, dearest comp</t>
+          <t>Published, cheapest comp</t>
         </is>
       </c>
       <c r="F11" s="11">
         <f>D11/B11-1</f>
+        <v>-0.1147730123</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...range high</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Published, dearest comp</t>
+        </is>
+      </c>
+      <c r="F12" s="11">
+        <f>D12/B12-1</f>
         <v>-0.115692829</v>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>LARGE box  46 x 39 x 36 in  -  89.19 sq ft of board per box</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Cost per box</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>100 each</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>250 each</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>1,000 each</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>Basis at 100</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>Change 100 -&gt; 1,000</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>PROVIDER - what we pay</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="n">
-        <v>38.89</v>
-      </c>
-      <c r="C39" s="9" t="n">
-        <v>25.61</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>ACTUAL invoice price</t>
-        </is>
-      </c>
-      <c r="F39" s="11">
-        <f>D39/B39-1</f>
-        <v>-0.5120572864</v>
-      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>ORCON - competing quote</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="C40" s="13" t="n">
-        <v>30.56</v>
-      </c>
-      <c r="D40" s="13" t="n">
-        <v>30.49</v>
+          <t>PROVIDER - what we pay</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>18.98</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>ACTUAL quote at 100</t>
+          <t>ACTUAL invoice price</t>
         </is>
       </c>
       <c r="F40" s="11">
         <f>D40/B40-1</f>
-        <v>-0.0066857073</v>
+        <v>-0.5120572864</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>Independent estimate</t>
-        </is>
-      </c>
-      <c r="B41" s="14" t="n">
-        <v>30.93</v>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>26.02</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>18.43</v>
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>ORCON - competing quote</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>30.49</v>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Modelled from research</t>
+          <t>ACTUAL quote at 100</t>
         </is>
       </c>
       <c r="F41" s="11">
         <f>D41/B41-1</f>
-        <v>-0.4040619607</v>
+        <v>-0.0066857073</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>Retail catalogue - mid of range</t>
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>ATLAS - competing quote</t>
         </is>
       </c>
       <c r="B42" s="14" t="n">
-        <v>37.26</v>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>35.56</v>
+        <v>19.83</v>
+      </c>
+      <c r="C42" s="15" t="n">
+        <v>18</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>32.96</v>
+        <v>17.09</v>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>Published, midpoint</t>
+          <t>ACTUAL quote at 250 (MOQ)</t>
         </is>
       </c>
       <c r="F42" s="11">
         <f>D42/B42-1</f>
-        <v>-0.1152538721</v>
+        <v>-0.1381412036</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ...range low</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="n">
-        <v>35.56</v>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>31.48</v>
+          <t>Independent estimate</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="n">
+        <v>30.93</v>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>18.43</v>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Published, cheapest comp</t>
+          <t>Modelled from research</t>
         </is>
       </c>
       <c r="F43" s="11">
         <f>D43/B43-1</f>
-        <v>-0.1147730123</v>
+        <v>-0.4040619607</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ...range high</t>
-        </is>
-      </c>
-      <c r="B44" s="14" t="n">
-        <v>38.96</v>
-      </c>
-      <c r="C44" s="14" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>34.45</v>
+          <t>Retail catalogue - mid of range</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="n">
+        <v>37.26</v>
+      </c>
+      <c r="C44" s="16" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>32.96</v>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>Published, dearest comp</t>
+          <t>Published, midpoint</t>
         </is>
       </c>
       <c r="F44" s="11">
         <f>D44/B44-1</f>
+        <v>-0.1152538721</v>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...range low</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>Published, cheapest comp</t>
+        </is>
+      </c>
+      <c r="F45" s="11">
+        <f>D45/B45-1</f>
+        <v>-0.1147730123</v>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ...range high</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Published, dearest comp</t>
+        </is>
+      </c>
+      <c r="F46" s="11">
+        <f>D46/B46-1</f>
         <v>-0.115692829</v>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>ACCEPTABLE PRICE AT 100 UNITS - and where we actually sit</t>
         </is>
       </c>
-      <c r="B70" s="4" t="n"/>
-      <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="n"/>
-      <c r="F70" s="4" t="n"/>
-      <c r="G70" s="4" t="n"/>
-      <c r="H70" s="5" t="n"/>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="5" t="n"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>Box</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>Ceiling</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>WE PAY</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>ORCON</t>
         </is>
       </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>vs ceiling</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>ATLAS*</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="26" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
+    <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>MEDIUM 39 x 20 x 32</t>
         </is>
       </c>
-      <c r="B72" s="14" t="n">
+      <c r="B74" s="16" t="n">
         <v>13.99</v>
       </c>
-      <c r="C72" s="14" t="n">
+      <c r="C74" s="16" t="n">
         <v>16.4</v>
       </c>
-      <c r="D72" s="14" t="n">
+      <c r="D74" s="16" t="n">
         <v>18.81</v>
       </c>
-      <c r="E72" s="15" t="n">
+      <c r="E74" s="17" t="n">
         <v>30.22</v>
       </c>
-      <c r="F72" s="16" t="n">
+      <c r="F74" s="18" t="n">
         <v>14.94</v>
       </c>
-      <c r="G72" s="17">
-        <f>E72-D72</f>
-        <v>11.4120225</v>
-      </c>
-      <c r="H72" s="18" t="inlineStr">
-        <is>
-          <t>OVER the ceiling. OrCon is $15.28 cheaper.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="26" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
+      <c r="G74" s="19" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="H74" s="20" t="inlineStr">
+        <is>
+          <t>OVER the ceiling. Atlas is $19.07 cheaper than us, OrCon $15.28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="26" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>LARGE 46 x 39 x 36</t>
         </is>
       </c>
-      <c r="B73" s="14" t="n">
+      <c r="B75" s="16" t="n">
         <v>30.93</v>
       </c>
-      <c r="C73" s="14" t="n">
+      <c r="C75" s="16" t="n">
         <v>34.94</v>
       </c>
-      <c r="D73" s="14" t="n">
+      <c r="D75" s="16" t="n">
         <v>38.96</v>
       </c>
-      <c r="E73" s="15" t="n">
+      <c r="E75" s="17" t="n">
         <v>38.89</v>
       </c>
-      <c r="F73" s="16" t="n">
+      <c r="F75" s="18" t="n">
         <v>30.7</v>
       </c>
-      <c r="G73" s="19">
-        <f>E73-D73</f>
-        <v>-0.0658072917</v>
-      </c>
-      <c r="H73" s="20" t="inlineStr">
-        <is>
-          <t>Top of the range. OrCon is $8.19 cheaper.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="56" customHeight="1">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="G75" s="19" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="H75" s="21" t="inlineStr">
+        <is>
+          <t>Top of the range. Atlas is $19.06 cheaper than us, OrCon $8.19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="56" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>HOW THE RANGE IS DEFINED. The FLOOR is the independent converter-direct estimate - below it is implausible for a custom job. The CEILING is the dearest comparable box anyone publishes: pay more than that and we are paying above retail for custom work, which is never defensible. TARGET is the midpoint. Bringing both boxes to the ceiling saves $1,141 on the current order (17%); to target, $1,777 (26%). Almost all of it is the medium box.</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="3" t="inlineStr">
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>WHAT THE THREE SCENARIOS SHOW</t>
         </is>
       </c>
-      <c r="B98" s="4" t="n"/>
-      <c r="C98" s="4" t="n"/>
-      <c r="D98" s="4" t="n"/>
-      <c r="E98" s="4" t="n"/>
-      <c r="F98" s="4" t="n"/>
-      <c r="G98" s="4" t="n"/>
-      <c r="H98" s="5" t="n"/>
-    </row>
-    <row r="99" ht="50" customHeight="1">
-      <c r="A99" s="21" t="inlineStr">
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="n"/>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="n"/>
+      <c r="H100" s="5" t="n"/>
+    </row>
+    <row r="101" ht="50" customHeight="1">
+      <c r="A101" s="22" t="inlineStr">
         <is>
           <t>At 100 each - today</t>
         </is>
       </c>
-      <c r="B99" s="22" t="n"/>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="B101" s="23" t="n"/>
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>The MEDIUM box is the outlier: $30.22 against a catalogue price of $17.99 for a comparable stock box. We pay $12.23 more per box than we could buy one for. The LARGE box at $38.89 is already fractionally BELOW its catalogue equivalent, so there is no case to answer there.</t>
         </is>
       </c>
-      <c r="D99" s="22" t="n"/>
-      <c r="E99" s="22" t="n"/>
-      <c r="F99" s="22" t="n"/>
-      <c r="G99" s="22" t="n"/>
-      <c r="H99" s="22" t="n"/>
-    </row>
-    <row r="100" ht="50" customHeight="1">
-      <c r="A100" s="21" t="inlineStr">
+      <c r="D101" s="23" t="n"/>
+      <c r="E101" s="23" t="n"/>
+      <c r="F101" s="23" t="n"/>
+      <c r="G101" s="23" t="n"/>
+      <c r="H101" s="23" t="n"/>
+    </row>
+    <row r="102" ht="50" customHeight="1">
+      <c r="A102" s="22" t="inlineStr">
         <is>
           <t>At 250 each - the crossover</t>
         </is>
       </c>
-      <c r="B100" s="22" t="n"/>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="B102" s="23" t="n"/>
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>The medium box drops to $16.94, inside its $16.45-$17.88 range. The large box at $25.61 falls clear BELOW its $34.07-$37.04 range. Both come good, and it takes only 150 more units of each to get here.</t>
         </is>
       </c>
-      <c r="D100" s="22" t="n"/>
-      <c r="E100" s="22" t="n"/>
-      <c r="F100" s="22" t="n"/>
-      <c r="G100" s="22" t="n"/>
-      <c r="H100" s="22" t="n"/>
-    </row>
-    <row r="101" ht="50" customHeight="1">
-      <c r="A101" s="21" t="inlineStr">
+      <c r="D102" s="23" t="n"/>
+      <c r="E102" s="23" t="n"/>
+      <c r="F102" s="23" t="n"/>
+      <c r="G102" s="23" t="n"/>
+      <c r="H102" s="23" t="n"/>
+    </row>
+    <row r="103" ht="50" customHeight="1">
+      <c r="A103" s="22" t="inlineStr">
         <is>
           <t>At 1,000 each - clearly good value</t>
         </is>
       </c>
-      <c r="B101" s="22" t="n"/>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="B103" s="23" t="n"/>
+      <c r="C103" s="10" t="inlineStr">
         <is>
           <t>Both boxes well below anything published: medium $10.31 vs $15.20-$16.63, large $18.98 vs $31.48-$34.45. Our price falls 66% and 51% from the 100-unit level while the published range moves only about 12% - retail discounts very little for volume, and that divergence is the whole argument.</t>
         </is>
       </c>
-      <c r="D101" s="22" t="n"/>
-      <c r="E101" s="22" t="n"/>
-      <c r="F101" s="22" t="n"/>
-      <c r="G101" s="22" t="n"/>
-      <c r="H101" s="22" t="n"/>
-    </row>
-    <row r="102" ht="50" customHeight="1">
-      <c r="A102" s="21" t="inlineStr">
+      <c r="D103" s="23" t="n"/>
+      <c r="E103" s="23" t="n"/>
+      <c r="F103" s="23" t="n"/>
+      <c r="G103" s="23" t="n"/>
+      <c r="H103" s="23" t="n"/>
+    </row>
+    <row r="104" ht="50" customHeight="1">
+      <c r="A104" s="22" t="inlineStr">
         <is>
           <t>The conclusion</t>
         </is>
       </c>
-      <c r="B102" s="22" t="n"/>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="B104" s="23" t="n"/>
+      <c r="C104" s="10" t="inlineStr">
         <is>
           <t>This is not a supplier problem, it is an order-size problem. Our provider's underlying board rate works out at about $188/MSF, which is competitive. What makes 100 units look expensive is roughly $2,213 per SKU of fixed cost spread over too few boxes - and it lands hardest on the smaller box, because fixed cost does not care how big the box is.</t>
         </is>
       </c>
-      <c r="D102" s="22" t="n"/>
-      <c r="E102" s="22" t="n"/>
-      <c r="F102" s="22" t="n"/>
-      <c r="G102" s="22" t="n"/>
-      <c r="H102" s="22" t="n"/>
+      <c r="D104" s="23" t="n"/>
+      <c r="E104" s="23" t="n"/>
+      <c r="F104" s="23" t="n"/>
+      <c r="G104" s="23" t="n"/>
+      <c r="H104" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A70:H70"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A100:H100"/>
     <mergeCell ref="A101:B101"/>
-    <mergeCell ref="C99:H99"/>
-    <mergeCell ref="A96:H96"/>
+    <mergeCell ref="C103:H103"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A72:H72"/>
     <mergeCell ref="C102:H102"/>
+    <mergeCell ref="A103:B103"/>
     <mergeCell ref="A98:H98"/>
     <mergeCell ref="C101:H101"/>
     <mergeCell ref="A102:B102"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="C100:H100"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -2265,7 +2377,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Us $ per set</t>
+          <t>Us $/set</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -2275,7 +2387,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>OrCon $ per set</t>
+          <t>OrCon $/set</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -2285,94 +2397,97 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>of which board (us)</t>
+          <t>ATLAS $/set</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>of which fixed (us)</t>
+          <t>ATLAS TOTAL</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>100 of each</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="25" t="n">
         <v>69.11</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <f>100*B6</f>
         <v>6911.0</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="27" t="n">
         <v>45.64</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <f>100*D6</f>
         <v>4564.0</v>
       </c>
-      <c r="F6" s="25" t="n">
-        <v>2486</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>4425</v>
+      <c r="F6" s="28" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="G6" s="26">
+        <f>100*F6</f>
+        <v>3097.168793045</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>250 of each</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="16" t="n">
         <v>42.56</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="30">
         <f>250*B7</f>
         <v>10639.5307101727</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="31" t="n">
         <v>45.37</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="30">
         <f>250*D7</f>
         <v>11341.5829287569</v>
       </c>
       <c r="F7" s="28" t="n">
-        <v>6214</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>4425</v>
+        <v>27.32</v>
+      </c>
+      <c r="G7" s="26">
+        <f>250*F7</f>
+        <v>6830.0</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>1000 of each</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="16" t="n">
         <v>29.28</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="30">
         <f>1000*B8</f>
         <v>29282.1842610365</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="31" t="n">
         <v>45.23</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="30">
         <f>1000*D8</f>
         <v>45229.4975725415</v>
       </c>
-      <c r="F8" s="28" t="n">
-        <v>24857</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>4425</v>
+      <c r="F8" s="32" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="G8" s="30">
+        <f>1000*F8</f>
+        <v>25494.1560347748</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -2394,19 +2509,19 @@
           <t>Going from 100 to 250 each</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n"/>
+      <c r="B35" s="23" t="n"/>
       <c r="C35" s="10" t="inlineStr">
         <is>
           <t>150 more sets, costing $3,729 more in total</t>
         </is>
       </c>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="30">
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="33">
         <f> $24.86 per additional set</f>
         <v/>
       </c>
-      <c r="F35" s="22" t="n"/>
-      <c r="G35" s="22" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
@@ -2414,19 +2529,19 @@
           <t>Going from 250 to 1000 each</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n"/>
+      <c r="B36" s="23" t="n"/>
       <c r="C36" s="10" t="inlineStr">
         <is>
           <t>750 more sets, costing $18,643 more in total</t>
         </is>
       </c>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="30">
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="33">
         <f> $24.86 per additional set</f>
         <v/>
       </c>
-      <c r="F36" s="22" t="n"/>
-      <c r="G36" s="22" t="n"/>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="23" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -2434,19 +2549,19 @@
           <t>Going from 100 to 1000 each</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n"/>
+      <c r="B37" s="23" t="n"/>
       <c r="C37" s="10" t="inlineStr">
         <is>
           <t>900 more sets, costing $22,371 more in total</t>
         </is>
       </c>
-      <c r="D37" s="22" t="n"/>
-      <c r="E37" s="30">
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="33">
         <f> $24.86 per additional set</f>
         <v/>
       </c>
-      <c r="F37" s="22" t="n"/>
-      <c r="G37" s="22" t="n"/>
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="23" t="n"/>
     </row>
     <row r="39" ht="52" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -2534,12 +2649,12 @@
           <t>Provider price, MEDIUM, 100 each</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>$30.22</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
@@ -2556,12 +2671,12 @@
           <t>Provider price, LARGE, 100 each</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>$38.89</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
@@ -2578,12 +2693,12 @@
           <t>Board area per box</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>43.06 / 89.19 sq ft</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>CALCULATED</t>
         </is>
@@ -2600,12 +2715,12 @@
           <t>Catalogue RANGE, 100 / 250 / 1,000</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>$399-437 / $382-415 / $353-386 per MSF</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>PUBLISHED</t>
         </is>
@@ -2622,12 +2737,12 @@
           <t>Independent estimate</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>$290-$180 / $330-$205 per MSF</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>MODELLED</t>
         </is>
@@ -2644,12 +2759,12 @@
           <t>Provider marginal board rate</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>$188 per MSF</t>
         </is>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
@@ -2666,12 +2781,12 @@
           <t>Provider fixed charge</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>$2,213 per SKU</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
@@ -2688,12 +2803,12 @@
           <t>Provider prices at 250 and 1,000</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>see Scenarios tab</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
@@ -2710,12 +2825,12 @@
           <t>OrCon quote, 100 each</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>med $14.94 / lge $30.70</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
@@ -2732,12 +2847,12 @@
           <t>OrCon pricing structure</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>$342/MSF + ~$23 fixed per SKU</t>
         </is>
       </c>
-      <c r="C14" s="33" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>DEDUCED</t>
         </is>
@@ -2754,12 +2869,12 @@
           <t>Estimate validated against OrCon</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>within 7%% and 1%%</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>CHECK</t>
         </is>
@@ -2776,12 +2891,12 @@
           <t>Acceptable range at 100</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>med $13.99-$18.81 / lge $30.93-$38.96</t>
         </is>
       </c>
-      <c r="C16" s="33" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
@@ -2798,12 +2913,12 @@
           <t>Freight</t>
         </is>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>excluded throughout</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
